--- a/out.xlsx
+++ b/out.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12420" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="12420" windowWidth="28125"/>
   </bookViews>
   <sheets>
     <sheet name="爆气表说明" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0_);[Red]\(0.0\)"/>
-    <numFmt numFmtId="165" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt formatCode="0.0_);[Red]\(0.0\)" numFmtId="164"/>
+    <numFmt formatCode="0.00_);[Red]\(0.00\)" numFmtId="165"/>
   </numFmts>
   <fonts count="50">
     <font>
@@ -1756,1265 +1756,1265 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="42">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="51" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="51" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="52" borderId="54" applyAlignment="1">
+    <xf applyAlignment="1" borderId="54" fillId="52" fontId="26" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="44">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="56" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="56" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="59" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="59" fontId="28" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="43">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="64" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="64" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="30" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="31" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="55" applyAlignment="1">
+    <xf applyAlignment="1" borderId="55" fillId="55" fontId="0" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="61" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="61" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="32" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="33" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="34" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="37" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="58" applyAlignment="1">
+    <xf applyAlignment="1" borderId="58" fillId="0" fontId="39" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="58" applyAlignment="1">
+    <xf applyAlignment="1" borderId="58" fillId="0" fontId="40" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="69" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="69" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="59" applyAlignment="1">
+    <xf applyAlignment="1" borderId="59" fillId="0" fontId="32" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="65" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="65" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="38" borderId="57" applyAlignment="1">
+    <xf applyAlignment="1" borderId="57" fillId="38" fontId="38" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="54" applyAlignment="1">
+    <xf applyAlignment="1" borderId="54" fillId="38" fontId="36" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="67" borderId="56" applyAlignment="1">
+    <xf applyAlignment="1" borderId="56" fillId="67" fontId="35" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="71" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="71" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="60" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="60" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="53" applyAlignment="1">
+    <xf applyAlignment="1" borderId="53" fillId="0" fontId="25" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="60" applyAlignment="1">
+    <xf applyAlignment="1" borderId="60" fillId="0" fontId="41" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="74" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="74" fontId="42" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="63" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="63" fontId="29" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="66" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="66" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="75" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="75" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="58" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="58" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="76" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="76" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="77" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="77" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="70" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="70" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="78" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="78" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="80" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="80" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="73" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="73" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyProtection="1">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="72" borderId="0" applyAlignment="1">
+    <xf applyProtection="1" borderId="0" fillId="0" fontId="13" numFmtId="0">
+      <protection hidden="0" locked="0"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="72" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="79" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="79" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="54" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="54" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="68" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="68" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="53" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="53" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="57" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="57" fontId="24" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="62" borderId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="62" fontId="27" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="373">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="3" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="3" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="3" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="4" numFmtId="49" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="5" numFmtId="49" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="49" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="3" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="3" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="3" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="49" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="49" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="49" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="3" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="4" numFmtId="49" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="13" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="13" numFmtId="1" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="5" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="6" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="7" fillId="7" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="8" fillId="7" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="9" fillId="7" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="0" fillId="7" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="7" fillId="6" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="8" fillId="6" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="10" fillId="8" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="12" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="13" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="14" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="15" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="9" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="9" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="9" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="10" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="10" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="18" fillId="10" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="19" fillId="10" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="17" fillId="10" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="18" fillId="10" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="11" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="11" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="18" fillId="11" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="19" fillId="11" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="17" fillId="11" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="18" fillId="11" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="12" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="12" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="18" fillId="12" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="19" fillId="12" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="17" fillId="12" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="18" fillId="12" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="13" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="13" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="13" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="14" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="14" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="14" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="15" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="15" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="16" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="16" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="17" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="17" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="17" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="18" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="18" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="18" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="16" fillId="19" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="19" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="19" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="20" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="21" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="20" fillId="20" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="21" fillId="20" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="7" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="8" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="9" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="14" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="15" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="5" fillId="0" fontId="20" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="22" fillId="0" fontId="20" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="23" fillId="0" fontId="20" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="7" fillId="22" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="8" fillId="22" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="24" fillId="22" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="25" fillId="22" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="26" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="27" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="9" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="14" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="15" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="27" fillId="8" fontId="21" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="8" fontId="21" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="15" fillId="8" fontId="21" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="28" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="7" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="8" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="29" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="7" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="30" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="31" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="32" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="10" fillId="24" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="24" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="33" fillId="24" fontId="3" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="24" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="34" fillId="24" fontId="3" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="24" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="24" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="36" fillId="24" fontId="3" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="24" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="24" fontId="3" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="24" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="38" fillId="25" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="26" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="33" fillId="26" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="26" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="34" fillId="26" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="39" fillId="26" fontId="23" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="38" fillId="27" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="28" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="33" fillId="28" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="28" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="34" fillId="28" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="39" fillId="28" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="38" fillId="29" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="30" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="33" fillId="30" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="30" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="34" fillId="30" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="30" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="30" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="30" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="30" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="19" fillId="30" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="38" fillId="31" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="32" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="32" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="32" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="19" fillId="32" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="32" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="26" fillId="33" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="34" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="34" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="34" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="19" fillId="34" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="34" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="10" fillId="35" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="35" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="35" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="35" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="19" fillId="35" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="35" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="40" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="10" fillId="36" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="36" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="36" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="36" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="19" fillId="36" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="36" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="41" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="42" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="39" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="9" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="38" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="41" fillId="38" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="38" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="42" fillId="38" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="38" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="39" fillId="38" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="39" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="10" fillId="39" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="39" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="39" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="39" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="39" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="40" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="10" fillId="40" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="40" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="40" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="40" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="19" fillId="40" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="40" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="40" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="41" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="10" fillId="41" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="41" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="41" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="41" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="41" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="13" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="10" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="14" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="16" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="17" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="9" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="0" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="43" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="18" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="38" fillId="42" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="42" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="42" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="42" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="44" fillId="42" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="17" fillId="19" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="30" fillId="42" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="32" fillId="42" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="45" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="43" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="46" fillId="43" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="43" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="43" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="43" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="43" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="43" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="48" fillId="43" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="45" fillId="20" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="10" fillId="24" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="24" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="24" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="24" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="24" fontId="4" numFmtId="1" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="29" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="43" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="10" fillId="42" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="42" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="44" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="49" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="19" fillId="44" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="44" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="44" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="44" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="44" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="44" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="35" fillId="44" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="45" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="45" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="45" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="45" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="45" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="45" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="45" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="48" fillId="45" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="46" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="46" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="46" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="46" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="46" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="46" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="46" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="48" fillId="46" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="37" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="37" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="48" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="47" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="47" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="47" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="47" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="47" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="47" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="47" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="48" fillId="47" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="46" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="46" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="29" fillId="22" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="40" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="19" fillId="40" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="40" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="40" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="40" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="40" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="50" fillId="22" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="48" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="48" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="48" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="48" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="48" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="48" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="48" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="32" fillId="48" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="49" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="46" fillId="49" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="49" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="49" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="49" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="49" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="49" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="32" fillId="49" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="50" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="46" fillId="50" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="50" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="50" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="50" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="50" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="50" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="48" fillId="50" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="46" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="48" fillId="37" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="46" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="0" fontId="5" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="32" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="51" fillId="8" fontId="21" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="43" fillId="8" fontId="21" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="37" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="49" fillId="8" fontId="21" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="52" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="52" fillId="0" fontId="5" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="52" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="49" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="13" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="72" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="8" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="29" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="72" fillId="23" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="24" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="24" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="25" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="50" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="30" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="31" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="32" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="11" fillId="24" fontId="3" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="22" fillId="26" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="34" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="9" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="46" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="36" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="37" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="48" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="42" fillId="26" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="22" fillId="28" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="61" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="42" fillId="28" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="22" fillId="30" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="67" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="42" fillId="30" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="30" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="22" fillId="32" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="19" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="11" fillId="32" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="34" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="34" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="35" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="35" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="36" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="36" fontId="22" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="17" fillId="38" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="15" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="18" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="41" fillId="38" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="39" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="10" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="39" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="40" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="11" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="40" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="41" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="12" fontId="19" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="11" fillId="41" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="66" fillId="42" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="42" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="11" fillId="42" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="71" fillId="42" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="47" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="62" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="43" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="21" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="45" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="47" fillId="43" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="62" fillId="20" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="24" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="14" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="49" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="11" fillId="24" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="44" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="62" fillId="21" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="43" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="11" fillId="44" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="45" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="45" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="46" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="46" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="46" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="46" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="37" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="37" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="47" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="47" fillId="47" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="5" fillId="22" fontId="15" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="48" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="48" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="17" fillId="49" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf borderId="63" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="64" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="37" fillId="49" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="17" fillId="50" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="73" fillId="8" fontId="18" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment horizontal="left" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="27" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="47" fillId="50" fontId="17" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="37" fillId="0" fontId="5" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+    <xf applyAlignment="1" borderId="74" fillId="8" fontId="21" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="2" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="51" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="52" fillId="0" fontId="5" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="3" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="4" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="3" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="3" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle builtinId="0" name="常规" xfId="0"/>
+    <cellStyle builtinId="7" name="货币[0]" xfId="1"/>
+    <cellStyle builtinId="38" name="20% - 强调文字颜色 3" xfId="2"/>
+    <cellStyle builtinId="20" name="输入" xfId="3"/>
+    <cellStyle builtinId="4" name="货币" xfId="4"/>
+    <cellStyle builtinId="6" name="千位分隔[0]" xfId="5"/>
+    <cellStyle builtinId="39" name="40% - 强调文字颜色 3" xfId="6"/>
+    <cellStyle builtinId="27" name="差" xfId="7"/>
+    <cellStyle builtinId="3" name="千位分隔" xfId="8"/>
+    <cellStyle builtinId="40" name="60% - 强调文字颜色 3" xfId="9"/>
+    <cellStyle builtinId="8" name="超链接" xfId="10"/>
+    <cellStyle builtinId="5" name="百分比" xfId="11"/>
+    <cellStyle builtinId="9" name="已访问的超链接" xfId="12"/>
+    <cellStyle builtinId="10" name="注释" xfId="13"/>
+    <cellStyle builtinId="36" name="60% - 强调文字颜色 2" xfId="14"/>
+    <cellStyle builtinId="19" name="标题 4" xfId="15"/>
+    <cellStyle builtinId="11" name="警告文本" xfId="16"/>
+    <cellStyle builtinId="15" name="标题" xfId="17"/>
+    <cellStyle builtinId="53" name="解释性文本" xfId="18"/>
+    <cellStyle builtinId="16" name="标题 1" xfId="19"/>
+    <cellStyle builtinId="17" name="标题 2" xfId="20"/>
+    <cellStyle builtinId="32" name="60% - 强调文字颜色 1" xfId="21"/>
+    <cellStyle builtinId="18" name="标题 3" xfId="22"/>
+    <cellStyle builtinId="44" name="60% - 强调文字颜色 4" xfId="23"/>
+    <cellStyle builtinId="21" name="输出" xfId="24"/>
+    <cellStyle builtinId="22" name="计算" xfId="25"/>
+    <cellStyle builtinId="23" name="检查单元格" xfId="26"/>
+    <cellStyle builtinId="50" name="20% - 强调文字颜色 6" xfId="27"/>
+    <cellStyle builtinId="33" name="强调文字颜色 2" xfId="28"/>
+    <cellStyle builtinId="24" name="链接单元格" xfId="29"/>
+    <cellStyle builtinId="25" name="汇总" xfId="30"/>
+    <cellStyle builtinId="26" name="好" xfId="31"/>
+    <cellStyle builtinId="28" name="适中" xfId="32"/>
+    <cellStyle builtinId="46" name="20% - 强调文字颜色 5" xfId="33"/>
+    <cellStyle builtinId="29" name="强调文字颜色 1" xfId="34"/>
+    <cellStyle builtinId="30" name="20% - 强调文字颜色 1" xfId="35"/>
+    <cellStyle builtinId="31" name="40% - 强调文字颜色 1" xfId="36"/>
+    <cellStyle builtinId="34" name="20% - 强调文字颜色 2" xfId="37"/>
+    <cellStyle builtinId="35" name="40% - 强调文字颜色 2" xfId="38"/>
+    <cellStyle builtinId="37" name="强调文字颜色 3" xfId="39"/>
+    <cellStyle builtinId="41" name="强调文字颜色 4" xfId="40"/>
+    <cellStyle builtinId="42" name="20% - 强调文字颜色 4" xfId="41"/>
     <cellStyle name="Normal 2" xfId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="43" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="44" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="45" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="46" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="47" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
+    <cellStyle builtinId="43" name="40% - 强调文字颜色 4" xfId="43"/>
+    <cellStyle builtinId="45" name="强调文字颜色 5" xfId="44"/>
+    <cellStyle builtinId="47" name="40% - 强调文字颜色 5" xfId="45"/>
+    <cellStyle builtinId="48" name="60% - 强调文字颜色 5" xfId="46"/>
+    <cellStyle builtinId="49" name="强调文字颜色 6" xfId="47"/>
+    <cellStyle builtinId="51" name="40% - 强调文字颜色 6" xfId="48"/>
+    <cellStyle builtinId="52" name="60% - 强调文字颜色 6" xfId="49"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -3032,7 +3032,7 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -3121,7 +3121,7 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Picture 8" descr=" "/>
+        <cNvPr descr=" " id="2" name="Picture 8"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3140,7 +3140,7 @@
           <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng">
+        <a:ln cap="flat" cmpd="sng" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3163,12 +3163,12 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="图片 2" descr=" "/>
+        <cNvPr descr=" " id="3" name="图片 2"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip r:embed="rId2"/>
-        <a:srcRect l="4259" t="3170" r="3099" b="4206"/>
+        <a:srcRect b="4206" l="4259" r="3099" t="3170"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3182,7 +3182,7 @@
           <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng">
+        <a:ln cap="flat" cmpd="sng" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3205,7 +3205,7 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="图片 3" descr=" "/>
+        <cNvPr descr=" " id="4" name="图片 3"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3224,7 +3224,7 @@
           <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng">
+        <a:ln cap="flat" cmpd="sng" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3247,7 +3247,7 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="图片 4" descr="wJAdU8I"/>
+        <cNvPr descr="wJAdU8I" id="5" name="图片 4"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3266,7 +3266,7 @@
           <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng">
+        <a:ln cap="flat" cmpd="sng" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3289,7 +3289,7 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Picture 8" descr=" "/>
+        <cNvPr descr=" " id="6" name="Picture 8"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3308,7 +3308,7 @@
           <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng">
+        <a:ln cap="flat" cmpd="sng" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3331,12 +3331,12 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="图片 6" descr=" "/>
+        <cNvPr descr=" " id="7" name="图片 6"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip r:embed="rId6"/>
-        <a:srcRect l="4259" t="3170" r="3099" b="4206"/>
+        <a:srcRect b="4206" l="4259" r="3099" t="3170"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3350,7 +3350,7 @@
           <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng">
+        <a:ln cap="flat" cmpd="sng" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3373,7 +3373,7 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="图片 7" descr=" "/>
+        <cNvPr descr=" " id="8" name="图片 7"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3392,7 +3392,7 @@
           <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng">
+        <a:ln cap="flat" cmpd="sng" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3415,7 +3415,7 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="图片 8" descr="wJAdU8I"/>
+        <cNvPr descr="wJAdU8I" id="9" name="图片 8"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3434,7 +3434,7 @@
           <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng">
+        <a:ln cap="flat" cmpd="sng" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3452,7 +3452,7 @@
     <ext cx="13096875" cy="76200000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPr descr="Picture" id="9" name="Image 9"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3482,7 +3482,7 @@
     <ext cx="13096875" cy="76200000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr descr="Picture" id="1" name="Image 1"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3512,7 +3512,7 @@
     <ext cx="13096875" cy="76200000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr descr="Picture" id="1" name="Image 1"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3542,7 +3542,7 @@
     <ext cx="13096875" cy="76200000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr descr="Picture" id="1" name="Image 1"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3572,7 +3572,7 @@
     <ext cx="13096875" cy="76200000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr descr="Picture" id="1" name="Image 1"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -3855,19 +3855,19 @@
   <dimension ref="A1:T85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.641666666666669" defaultRowHeight="14.25"/>
   <cols>
-    <col width="9.275" customWidth="1" style="66" min="1" max="4"/>
-    <col width="18" customWidth="1" style="66" min="5" max="5"/>
-    <col width="9.275" customWidth="1" style="66" min="6" max="8"/>
-    <col width="26.725" customWidth="1" style="66" min="9" max="9"/>
-    <col width="14.0416666666667" customWidth="1" style="65" min="10" max="10"/>
-    <col width="16.0916666666667" customWidth="1" style="297" min="11" max="11"/>
-    <col width="19.0916666666667" customWidth="1" style="68" min="12" max="12"/>
-    <col width="52.775" customWidth="1" style="65" min="13" max="13"/>
-    <col width="9.275" customWidth="1" style="66" min="14" max="1026"/>
-    <col width="9.824999999999999" customWidth="1" style="66" min="1027" max="16384"/>
+    <col customWidth="1" max="4" min="1" style="66" width="9.275"/>
+    <col customWidth="1" max="5" min="5" style="66" width="18"/>
+    <col customWidth="1" max="8" min="6" style="66" width="9.275"/>
+    <col customWidth="1" max="9" min="9" style="66" width="26.725"/>
+    <col customWidth="1" max="10" min="10" style="65" width="14.0416666666667"/>
+    <col customWidth="1" max="11" min="11" style="297" width="16.0916666666667"/>
+    <col customWidth="1" max="12" min="12" style="68" width="19.0916666666667"/>
+    <col customWidth="1" max="13" min="13" style="65" width="52.775"/>
+    <col customWidth="1" max="1026" min="14" style="66" width="9.275"/>
+    <col customWidth="1" max="16384" min="1027" style="66" width="9.824999999999999"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="1" s="298">
       <c r="A1" s="69" t="inlineStr">
         <is>
           <t>2022年S3赛季星弹二模爆气表说明</t>
@@ -3890,7 +3890,7 @@
       <c r="L1" s="299" t="n"/>
       <c r="M1" s="300" t="n"/>
     </row>
-    <row r="2" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="2" s="298">
       <c r="A2" s="302" t="n"/>
       <c r="B2" s="303" t="n"/>
       <c r="C2" s="303" t="n"/>
@@ -3905,7 +3905,7 @@
       <c r="L2" s="306" t="n"/>
       <c r="M2" s="307" t="n"/>
     </row>
-    <row r="3" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="3" s="298">
       <c r="A3" s="71" t="inlineStr">
         <is>
           <t>此表包含S3赛季6-10星排位歌曲，测点为手打+机测最高分点。
@@ -3937,14 +3937,14 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="4" s="298">
       <c r="A4" s="310" t="n"/>
       <c r="J4" s="311" t="n"/>
       <c r="K4" s="312" t="n"/>
       <c r="L4" s="313" t="n"/>
       <c r="M4" s="314" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="5" s="298">
       <c r="A5" s="75" t="inlineStr">
         <is>
           <t>爆气表描述说明</t>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="6" s="298">
       <c r="A6" s="77" t="inlineStr">
         <is>
           <t>爆点cb描述：
@@ -4011,7 +4011,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="7" s="298">
       <c r="A7" s="310" t="n"/>
       <c r="I7" s="318" t="n"/>
       <c r="J7" s="173" t="inlineStr">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="8" s="298">
       <c r="A8" s="310" t="n"/>
       <c r="I8" s="318" t="n"/>
       <c r="J8" s="173" t="inlineStr">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="9" s="298">
       <c r="A9" s="310" t="n"/>
       <c r="I9" s="318" t="n"/>
       <c r="J9" s="179" t="inlineStr">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="10" s="298">
       <c r="A10" s="310" t="n"/>
       <c r="I10" s="318" t="n"/>
       <c r="J10" s="183" t="inlineStr">
@@ -4091,7 +4091,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="11" s="298">
       <c r="A11" s="310" t="n"/>
       <c r="I11" s="318" t="n"/>
       <c r="J11" s="187" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="N11" s="65" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="12" s="298">
       <c r="A12" s="305" t="n"/>
       <c r="B12" s="306" t="n"/>
       <c r="C12" s="306" t="n"/>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="N12" s="65" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="13" s="298">
       <c r="A13" s="81" t="inlineStr">
         <is>
           <t>团队成员：</t>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="N13" s="65" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="14" s="298">
       <c r="A14" s="83" t="inlineStr">
         <is>
           <t>隼</t>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="N14" s="65" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="15" s="298">
       <c r="A15" s="86" t="inlineStr">
         <is>
           <t>当歌</t>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="N15" s="65" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="16" s="298">
       <c r="A16" s="92" t="inlineStr">
         <is>
           <t>东野</t>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="N16" s="65" t="n"/>
     </row>
-    <row r="17" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="17" s="298">
       <c r="A17" s="98" t="inlineStr">
         <is>
           <t>豆豆</t>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="N17" s="65" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="18" s="298">
       <c r="A18" s="104" t="inlineStr">
         <is>
           <t>猫猫</t>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="N18" s="65" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="19" s="298">
       <c r="A19" s="107" t="inlineStr">
         <is>
           <t>千弦</t>
@@ -4404,7 +4404,7 @@
       <c r="M19" s="300" t="n"/>
       <c r="N19" s="65" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="20" s="298">
       <c r="A20" s="110" t="inlineStr">
         <is>
           <t>青云</t>
@@ -4432,7 +4432,7 @@
       <c r="M20" s="307" t="n"/>
       <c r="N20" s="65" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="21" s="298">
       <c r="A21" s="114" t="inlineStr">
         <is>
           <t>思豆</t>
@@ -4460,7 +4460,7 @@
       <c r="M21" s="222" t="n"/>
       <c r="N21" s="65" t="n"/>
     </row>
-    <row r="22" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="22" s="298">
       <c r="A22" s="117" t="inlineStr">
         <is>
           <t>天天</t>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="N22" s="65" t="n"/>
     </row>
-    <row r="23" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="23" s="298">
       <c r="A23" s="120" t="inlineStr">
         <is>
           <t>云天</t>
@@ -4524,7 +4524,7 @@
       <c r="M23" s="307" t="n"/>
       <c r="N23" s="65" t="n"/>
     </row>
-    <row r="24" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="24" s="298">
       <c r="A24" s="339" t="inlineStr">
         <is>
           <t>打赏/赞助我们/向我们反馈</t>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N24" s="65" t="n"/>
     </row>
-    <row r="25" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="25" s="298">
       <c r="A25" s="343" t="inlineStr">
         <is>
           <t>做表不易，每一首歌的每一个点都要一遍遍手打asp、读分，找点，写入描述。我们需要你们的支持和鼓励！ Ԅ(¯﹃¯ԅ)</t>
@@ -4576,7 +4576,7 @@
       <c r="M25" s="314" t="n"/>
       <c r="N25" s="65" t="n"/>
     </row>
-    <row r="26" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="26" s="298">
       <c r="A26" s="344" t="n"/>
       <c r="B26" s="326" t="n"/>
       <c r="C26" s="326" t="n"/>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="N26" s="65" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="27" s="298">
       <c r="A27" s="347" t="inlineStr">
         <is>
           <t>*认为爆点指数低的，请优先对比对局结束后的指数是否达到表中已给的指数（对局指数是四舍五入结果），如果爆不到，请优先考虑延迟、压爆等问题。
@@ -4625,7 +4625,7 @@
       <c r="M27" s="314" t="n"/>
       <c r="N27" s="65" t="n"/>
     </row>
-    <row r="28" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="28" s="298">
       <c r="A28" s="310" t="n"/>
       <c r="I28" s="348" t="n"/>
       <c r="J28" s="242" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="N28" s="65" t="n"/>
     </row>
-    <row r="29" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="29" s="298">
       <c r="A29" s="344" t="n"/>
       <c r="B29" s="326" t="n"/>
       <c r="C29" s="326" t="n"/>
@@ -4661,7 +4661,7 @@
       <c r="L29" s="338" t="n"/>
       <c r="M29" s="314" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="30" s="298">
       <c r="A30" s="133" t="inlineStr">
         <is>
           <t xml:space="preserve">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="31" s="298">
       <c r="A31" s="310" t="n"/>
       <c r="I31" s="348" t="n"/>
       <c r="J31" s="313" t="n"/>
@@ -4703,7 +4703,7 @@
       <c r="L31" s="338" t="n"/>
       <c r="M31" s="314" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="32" s="298">
       <c r="A32" s="310" t="n"/>
       <c r="I32" s="348" t="n"/>
       <c r="J32" s="249" t="inlineStr">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="33" s="298">
       <c r="A33" s="310" t="n"/>
       <c r="I33" s="348" t="n"/>
       <c r="J33" s="351" t="inlineStr">
@@ -4743,7 +4743,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="34" s="298">
       <c r="A34" s="310" t="n"/>
       <c r="I34" s="348" t="n"/>
       <c r="J34" s="257" t="inlineStr">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="35" s="298">
       <c r="A35" s="302" t="n"/>
       <c r="B35" s="303" t="n"/>
       <c r="C35" s="303" t="n"/>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="36" s="298">
       <c r="A36" s="70" t="inlineStr">
         <is>
           <t>广告位邀租</t>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="37" s="298">
       <c r="A37" s="355" t="inlineStr">
         <is>
           <t>赞助我们后，可以将广告或宣传语打在备注栏内，我们将在下赛季表的首页列出您的id和宣传语。赞助金额高者可选择加彩加粗置顶显示。有意请联系QQ:384009605(๑╹◡╹)ﾉ"""</t>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="38" s="298">
       <c r="A38" s="302" t="n"/>
       <c r="B38" s="303" t="n"/>
       <c r="C38" s="303" t="n"/>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="39" s="298">
       <c r="A39" s="69" t="inlineStr">
         <is>
           <t>误差主要来源</t>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="40" s="298">
       <c r="A40" s="360" t="inlineStr">
         <is>
           <t>1. 存气结束时间估计误差
@@ -4947,7 +4947,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="41" s="298">
       <c r="A41" s="310" t="n"/>
       <c r="J41" s="283" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="42" s="298">
       <c r="A42" s="344" t="n"/>
       <c r="B42" s="326" t="n"/>
       <c r="C42" s="326" t="n"/>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="43" s="298">
       <c r="A43" s="69" t="inlineStr">
         <is>
           <t>更新日志</t>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="44" s="298">
       <c r="A44" s="364" t="inlineStr">
         <is>
           <t>2020.09.09 更新s9歌曲
@@ -5092,7 +5092,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="45" s="298">
       <c r="I45" s="348" t="n"/>
       <c r="J45" s="285" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="M45" s="288" t="n"/>
     </row>
-    <row r="46" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="46" s="298">
       <c r="I46" s="348" t="n"/>
       <c r="J46" s="285" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="47" s="298">
       <c r="I47" s="348" t="n"/>
       <c r="J47" s="285" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="48" s="298">
       <c r="I48" s="348" t="n"/>
       <c r="J48" s="285" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="M48" s="288" t="n"/>
     </row>
-    <row r="49" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="49" s="298">
       <c r="I49" s="348" t="n"/>
       <c r="J49" s="285" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="35.25" customHeight="1" s="298">
+    <row customHeight="1" ht="35.25" r="50" s="298">
       <c r="I50" s="348" t="n"/>
       <c r="J50" s="285" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="51" s="298">
       <c r="I51" s="348" t="n"/>
       <c r="J51" s="285" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="52" s="298">
       <c r="I52" s="348" t="n"/>
       <c r="J52" s="285" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="53" s="298">
       <c r="I53" s="348" t="n"/>
       <c r="J53" s="285" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="54" s="298">
       <c r="I54" s="348" t="n"/>
       <c r="J54" s="285" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="55" s="298">
       <c r="I55" s="348" t="n"/>
       <c r="J55" s="291" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="M55" s="288" t="n"/>
     </row>
-    <row r="56" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="56" s="298">
       <c r="I56" s="348" t="n"/>
       <c r="J56" s="291" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="57" s="298">
       <c r="I57" s="348" t="n"/>
       <c r="J57" s="291" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="58" s="298">
       <c r="I58" s="348" t="n"/>
       <c r="J58" s="291" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="59" s="298">
       <c r="I59" s="348" t="n"/>
       <c r="J59" s="291" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
       <c r="S59" s="64" t="n"/>
       <c r="T59" s="64" t="n"/>
     </row>
-    <row r="60" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="60" s="298">
       <c r="I60" s="348" t="n"/>
       <c r="J60" s="295" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
       <c r="S60" s="65" t="n"/>
       <c r="T60" s="65" t="n"/>
     </row>
-    <row r="61" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="61" s="298">
       <c r="I61" s="348" t="n"/>
       <c r="K61" s="65" t="n"/>
       <c r="L61" s="65" t="n"/>
@@ -5421,7 +5421,7 @@
       <c r="S61" s="65" t="n"/>
       <c r="T61" s="65" t="n"/>
     </row>
-    <row r="62" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="62" s="298">
       <c r="I62" s="348" t="n"/>
       <c r="K62" s="65" t="n"/>
       <c r="L62" s="65" t="n"/>
@@ -5432,7 +5432,7 @@
       <c r="S62" s="65" t="n"/>
       <c r="T62" s="65" t="n"/>
     </row>
-    <row r="63" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="63" s="298">
       <c r="A63" s="326" t="n"/>
       <c r="B63" s="326" t="n"/>
       <c r="C63" s="326" t="n"/>
@@ -5451,7 +5451,7 @@
       <c r="S63" s="65" t="n"/>
       <c r="T63" s="65" t="n"/>
     </row>
-    <row r="64" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="64" s="298">
       <c r="A64" s="65" t="n"/>
       <c r="B64" s="65" t="n"/>
       <c r="C64" s="65" t="n"/>
@@ -5470,7 +5470,7 @@
       <c r="S64" s="65" t="n"/>
       <c r="T64" s="65" t="n"/>
     </row>
-    <row r="65" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="65" s="298">
       <c r="A65" s="65" t="n"/>
       <c r="B65" s="65" t="n"/>
       <c r="C65" s="65" t="n"/>
@@ -5489,7 +5489,7 @@
       <c r="S65" s="65" t="n"/>
       <c r="T65" s="65" t="n"/>
     </row>
-    <row r="66" ht="30" customHeight="1" s="298">
+    <row customHeight="1" ht="30" r="66" s="298">
       <c r="A66" s="65" t="n"/>
       <c r="B66" s="65" t="n"/>
       <c r="C66" s="65" t="n"/>
@@ -5510,7 +5510,7 @@
       <c r="S66" s="65" t="n"/>
       <c r="T66" s="65" t="n"/>
     </row>
-    <row r="67" ht="30" customFormat="1" customHeight="1" s="63">
+    <row customFormat="1" customHeight="1" ht="30" r="67" s="63">
       <c r="A67" s="65" t="n"/>
       <c r="B67" s="65" t="n"/>
       <c r="C67" s="65" t="n"/>
@@ -5532,7 +5532,7 @@
       <c r="S67" s="65" t="n"/>
       <c r="T67" s="65" t="n"/>
     </row>
-    <row r="68" ht="30" customFormat="1" customHeight="1" s="63">
+    <row customFormat="1" customHeight="1" ht="30" r="68" s="63">
       <c r="A68" s="66" t="n"/>
       <c r="B68" s="66" t="n"/>
       <c r="C68" s="66" t="n"/>
@@ -5550,7 +5550,7 @@
       <c r="S68" s="65" t="n"/>
       <c r="T68" s="65" t="n"/>
     </row>
-    <row r="69" ht="30" customFormat="1" customHeight="1" s="63">
+    <row customFormat="1" customHeight="1" ht="30" r="69" s="63">
       <c r="A69" s="65" t="n"/>
       <c r="B69" s="65" t="n"/>
       <c r="C69" s="65" t="n"/>
@@ -5568,7 +5568,7 @@
       <c r="S69" s="65" t="n"/>
       <c r="T69" s="65" t="n"/>
     </row>
-    <row r="70" ht="30" customFormat="1" customHeight="1" s="63">
+    <row customFormat="1" customHeight="1" ht="30" r="70" s="63">
       <c r="A70" s="65" t="n"/>
       <c r="B70" s="65" t="n"/>
       <c r="C70" s="65" t="n"/>
@@ -5586,7 +5586,7 @@
       <c r="S70" s="65" t="n"/>
       <c r="T70" s="65" t="n"/>
     </row>
-    <row r="71" ht="30" customFormat="1" customHeight="1" s="63">
+    <row customFormat="1" customHeight="1" ht="30" r="71" s="63">
       <c r="A71" s="65" t="n"/>
       <c r="B71" s="65" t="n"/>
       <c r="C71" s="65" t="n"/>
@@ -5608,7 +5608,7 @@
       <c r="S71" s="65" t="n"/>
       <c r="T71" s="65" t="n"/>
     </row>
-    <row r="72" ht="30" customFormat="1" customHeight="1" s="63">
+    <row customFormat="1" customHeight="1" ht="30" r="72" s="63">
       <c r="A72" s="65" t="n"/>
       <c r="B72" s="65" t="n"/>
       <c r="C72" s="65" t="n"/>
@@ -5630,7 +5630,7 @@
       <c r="S72" s="65" t="n"/>
       <c r="T72" s="65" t="n"/>
     </row>
-    <row r="73" ht="39.95" customFormat="1" customHeight="1" s="64">
+    <row customFormat="1" customHeight="1" ht="39.95" r="73" s="64">
       <c r="A73" s="66" t="n"/>
       <c r="B73" s="66" t="n"/>
       <c r="C73" s="66" t="n"/>
@@ -5648,7 +5648,7 @@
       <c r="S73" s="65" t="n"/>
       <c r="T73" s="65" t="n"/>
     </row>
-    <row r="74" ht="39.95" customFormat="1" customHeight="1" s="64">
+    <row customFormat="1" customHeight="1" ht="39.95" r="74" s="64">
       <c r="A74" s="66" t="n"/>
       <c r="B74" s="66" t="n"/>
       <c r="C74" s="66" t="n"/>
@@ -5670,7 +5670,7 @@
       <c r="S74" s="65" t="n"/>
       <c r="T74" s="65" t="n"/>
     </row>
-    <row r="75" ht="30" customFormat="1" customHeight="1" s="64">
+    <row customFormat="1" customHeight="1" ht="30" r="75" s="64">
       <c r="A75" s="66" t="n"/>
       <c r="B75" s="66" t="n"/>
       <c r="C75" s="66" t="n"/>
@@ -5692,7 +5692,7 @@
       <c r="S75" s="65" t="n"/>
       <c r="T75" s="65" t="n"/>
     </row>
-    <row r="76" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="76" s="65">
       <c r="A76" s="66" t="n"/>
       <c r="B76" s="66" t="n"/>
       <c r="C76" s="66" t="n"/>
@@ -5704,7 +5704,7 @@
       <c r="I76" s="66" t="n"/>
       <c r="N76" s="66" t="n"/>
     </row>
-    <row r="77" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="77" s="65">
       <c r="A77" s="66" t="n"/>
       <c r="B77" s="66" t="n"/>
       <c r="C77" s="66" t="n"/>
@@ -5716,7 +5716,7 @@
       <c r="I77" s="66" t="n"/>
       <c r="N77" s="66" t="n"/>
     </row>
-    <row r="78" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="78" s="65">
       <c r="A78" s="66" t="n"/>
       <c r="B78" s="66" t="n"/>
       <c r="C78" s="66" t="n"/>
@@ -5728,7 +5728,7 @@
       <c r="I78" s="66" t="n"/>
       <c r="N78" s="66" t="n"/>
     </row>
-    <row r="79" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="79" s="65">
       <c r="A79" s="66" t="n"/>
       <c r="B79" s="66" t="n"/>
       <c r="C79" s="66" t="n"/>
@@ -5746,7 +5746,7 @@
       <c r="Q79" s="66" t="n"/>
       <c r="R79" s="66" t="n"/>
     </row>
-    <row r="80" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="80" s="65">
       <c r="A80" s="66" t="n"/>
       <c r="B80" s="66" t="n"/>
       <c r="C80" s="66" t="n"/>
@@ -5764,7 +5764,7 @@
       <c r="S80" s="66" t="n"/>
       <c r="T80" s="66" t="n"/>
     </row>
-    <row r="81" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="81" s="65">
       <c r="A81" s="66" t="n"/>
       <c r="B81" s="66" t="n"/>
       <c r="C81" s="66" t="n"/>
@@ -5782,7 +5782,7 @@
       <c r="S81" s="66" t="n"/>
       <c r="T81" s="66" t="n"/>
     </row>
-    <row r="82" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="82" s="65">
       <c r="A82" s="66" t="n"/>
       <c r="B82" s="66" t="n"/>
       <c r="C82" s="66" t="n"/>
@@ -5802,7 +5802,7 @@
       <c r="S82" s="66" t="n"/>
       <c r="T82" s="66" t="n"/>
     </row>
-    <row r="83" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="83" s="65">
       <c r="A83" s="66" t="n"/>
       <c r="B83" s="66" t="n"/>
       <c r="C83" s="66" t="n"/>
@@ -5822,7 +5822,7 @@
       <c r="S83" s="66" t="n"/>
       <c r="T83" s="66" t="n"/>
     </row>
-    <row r="84" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="84" s="65">
       <c r="A84" s="66" t="n"/>
       <c r="B84" s="66" t="n"/>
       <c r="C84" s="66" t="n"/>
@@ -5842,7 +5842,7 @@
       <c r="S84" s="66" t="n"/>
       <c r="T84" s="66" t="n"/>
     </row>
-    <row r="85" ht="30" customFormat="1" customHeight="1" s="65">
+    <row customFormat="1" customHeight="1" ht="30" r="85" s="65">
       <c r="A85" s="66" t="n"/>
       <c r="B85" s="66" t="n"/>
       <c r="C85" s="66" t="n"/>
@@ -5863,7 +5863,7 @@
       <c r="T85" s="66" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="0" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
+  <sheetProtection autoFilter="0" deleteColumns="1" deleteRows="1" formatCells="0" formatColumns="1" formatRows="1" insertColumns="1" insertHyperlinks="0" insertRows="1" objects="1" pivotTables="1" scenarios="0" selectLockedCells="0" selectUnlockedCells="0" sheet="1" sort="1"/>
   <mergeCells count="74">
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="K5:L5"/>
@@ -5940,7 +5940,7 @@
     <mergeCell ref="A40:I42"/>
     <mergeCell ref="A44:I63"/>
   </mergeCells>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.510416666666667" footer="0.510416666666667"/>
+  <pageMargins bottom="0.75" footer="0.510416666666667" header="0.510416666666667" left="0.699305555555556" right="0.699305555555556" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5954,19 +5954,19 @@
   <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.641666666666669" defaultRowHeight="14.25"/>
   <cols>
-    <col width="8.725" customWidth="1" style="1" min="1" max="2"/>
-    <col width="20.6333333333333" customWidth="1" style="1" min="3" max="3"/>
-    <col width="8.725" customWidth="1" style="1" min="4" max="4"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="5" max="5"/>
-    <col width="8.725" customWidth="1" style="1" min="6" max="6"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9.175000000000001" customWidth="1" style="1" min="8" max="8"/>
-    <col width="8.725" customWidth="1" style="2" min="9" max="10"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="11" max="11"/>
-    <col width="8.725" customWidth="1" style="1" min="12" max="256"/>
+    <col customWidth="1" max="2" min="1" style="1" width="8.725"/>
+    <col customWidth="1" max="3" min="3" style="1" width="20.6333333333333"/>
+    <col customWidth="1" max="4" min="4" style="1" width="8.725"/>
+    <col customWidth="1" max="5" min="5" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="6" min="6" style="1" width="8.725"/>
+    <col customWidth="1" max="7" min="7" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="8" min="8" style="1" width="9.175000000000001"/>
+    <col customWidth="1" max="10" min="9" style="2" width="8.725"/>
+    <col customWidth="1" max="11" min="11" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="256" min="12" style="1" width="8.725"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" customHeight="1" s="298">
+    <row customHeight="1" ht="40.5" r="1" s="298">
       <c r="A1" s="36" t="inlineStr">
         <is>
           <t>音序</t>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="2" s="298">
       <c r="A2" s="57" t="inlineStr">
         <is>
           <t>*</t>
@@ -6096,7 +6096,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="3" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="3" s="298">
       <c r="A3" s="57" t="inlineStr">
         <is>
           <t>A</t>
@@ -6158,7 +6158,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="4" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="4" s="298">
       <c r="A4" s="369" t="n"/>
       <c r="B4" s="8" t="n">
         <v>6</v>
@@ -6216,7 +6216,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="5" s="298">
       <c r="A5" s="57" t="inlineStr">
         <is>
           <t>B</t>
@@ -6278,7 +6278,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="6" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="6" s="298">
       <c r="A6" s="370" t="n"/>
       <c r="B6" s="8" t="n">
         <v>6</v>
@@ -6336,7 +6336,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="7" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="7" s="298">
       <c r="A7" s="370" t="n"/>
       <c r="B7" s="8" t="n">
         <v>7</v>
@@ -6394,7 +6394,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="8" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="8" s="298">
       <c r="A8" s="370" t="n"/>
       <c r="B8" s="46" t="n">
         <v>7</v>
@@ -6452,7 +6452,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="9" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="9" s="298">
       <c r="A9" s="370" t="n"/>
       <c r="B9" s="8" t="n">
         <v>6</v>
@@ -6510,7 +6510,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="10" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="10" s="298">
       <c r="A10" s="370" t="n"/>
       <c r="B10" s="8" t="n">
         <v>6</v>
@@ -6568,7 +6568,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="11" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="11" s="298">
       <c r="A11" s="370" t="n"/>
       <c r="B11" s="8" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="12" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="12" s="298">
       <c r="A12" s="370" t="n"/>
       <c r="B12" s="8" t="n">
         <v>7</v>
@@ -6684,7 +6684,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="13" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="13" s="298">
       <c r="A13" s="370" t="n"/>
       <c r="B13" s="8" t="n">
         <v>6</v>
@@ -6742,7 +6742,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="14" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="14" s="298">
       <c r="A14" s="370" t="n"/>
       <c r="B14" s="8" t="n">
         <v>6</v>
@@ -6800,7 +6800,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="15" s="298">
       <c r="A15" s="370" t="n"/>
       <c r="B15" s="8" t="n">
         <v>6</v>
@@ -6858,7 +6858,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="16" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="16" s="298">
       <c r="A16" s="369" t="n"/>
       <c r="B16" s="8" t="n">
         <v>7</v>
@@ -6916,7 +6916,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="17" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="17" s="298">
       <c r="A17" s="57" t="inlineStr">
         <is>
           <t>C</t>
@@ -6978,7 +6978,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="18" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="18" s="298">
       <c r="A18" s="370" t="n"/>
       <c r="B18" s="8" t="n">
         <v>7</v>
@@ -7036,7 +7036,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="19" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="19" s="298">
       <c r="A19" s="369" t="n"/>
       <c r="B19" s="8" t="n">
         <v>6</v>
@@ -7094,7 +7094,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="20" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="20" s="298">
       <c r="A20" s="57" t="inlineStr">
         <is>
           <t>D</t>
@@ -7156,7 +7156,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="21" ht="94.5" customHeight="1" s="298">
+    <row customHeight="1" ht="94.5" r="21" s="298">
       <c r="A21" s="369" t="n"/>
       <c r="B21" s="8" t="n">
         <v>7</v>
@@ -7224,7 +7224,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="22" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="22" s="298">
       <c r="A22" s="57" t="inlineStr">
         <is>
           <t>F</t>
@@ -7286,7 +7286,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="23" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="23" s="298">
       <c r="A23" s="369" t="n"/>
       <c r="B23" s="8" t="n">
         <v>6</v>
@@ -7344,7 +7344,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="24" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="24" s="298">
       <c r="A24" s="57" t="inlineStr">
         <is>
           <t>G</t>
@@ -7406,7 +7406,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="25" s="298">
       <c r="A25" s="370" t="n"/>
       <c r="B25" s="8" t="n">
         <v>6</v>
@@ -7464,7 +7464,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="26" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="26" s="298">
       <c r="A26" s="370" t="n"/>
       <c r="B26" s="8" t="n">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="27" ht="126" customHeight="1" s="298">
+    <row customHeight="1" ht="126" r="27" s="298">
       <c r="A27" s="369" t="n"/>
       <c r="B27" s="8" t="n">
         <v>6</v>
@@ -7590,7 +7590,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="28" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="28" s="298">
       <c r="A28" s="57" t="inlineStr">
         <is>
           <t>H</t>
@@ -7652,7 +7652,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="29" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="29" s="298">
       <c r="A29" s="370" t="n"/>
       <c r="B29" s="8" t="n">
         <v>6</v>
@@ -7710,7 +7710,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="30" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="30" s="298">
       <c r="A30" s="370" t="n"/>
       <c r="B30" s="46" t="n">
         <v>7</v>
@@ -7768,7 +7768,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="31" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="31" s="298">
       <c r="A31" s="370" t="n"/>
       <c r="B31" s="8" t="n">
         <v>7</v>
@@ -7826,7 +7826,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="32" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="32" s="298">
       <c r="A32" s="370" t="n"/>
       <c r="B32" s="8" t="n">
         <v>7</v>
@@ -7884,7 +7884,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="33" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="33" s="298">
       <c r="A33" s="370" t="n"/>
       <c r="B33" s="8" t="n">
         <v>7</v>
@@ -7942,7 +7942,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="34" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="34" s="298">
       <c r="A34" s="370" t="n"/>
       <c r="B34" s="8" t="n">
         <v>6</v>
@@ -8000,7 +8000,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="35" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="35" s="298">
       <c r="A35" s="369" t="n"/>
       <c r="B35" s="8" t="n">
         <v>7</v>
@@ -8058,7 +8058,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="36" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="36" s="298">
       <c r="A36" s="57" t="inlineStr">
         <is>
           <t>I</t>
@@ -8120,7 +8120,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="37" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="37" s="298">
       <c r="A37" s="57" t="inlineStr">
         <is>
           <t>J</t>
@@ -8182,7 +8182,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="38" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="38" s="298">
       <c r="A38" s="370" t="n"/>
       <c r="B38" s="8" t="n">
         <v>7</v>
@@ -8240,7 +8240,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="39" s="298">
       <c r="A39" s="370" t="n"/>
       <c r="B39" s="8" t="n">
         <v>6</v>
@@ -8298,7 +8298,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="40" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="40" s="298">
       <c r="A40" s="369" t="n"/>
       <c r="B40" s="8" t="n">
         <v>6</v>
@@ -8356,7 +8356,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="41" ht="110.25" customHeight="1" s="298">
+    <row customHeight="1" ht="110.25" r="41" s="298">
       <c r="A41" s="57" t="inlineStr">
         <is>
           <t>K</t>
@@ -8428,7 +8428,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="42" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="42" s="298">
       <c r="A42" s="370" t="n"/>
       <c r="B42" s="8" t="n">
         <v>6</v>
@@ -8486,7 +8486,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="43" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="43" s="298">
       <c r="A43" s="370" t="n"/>
       <c r="B43" s="8" t="n">
         <v>7</v>
@@ -8544,7 +8544,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="44" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="44" s="298">
       <c r="A44" s="369" t="n"/>
       <c r="B44" s="46" t="n">
         <v>7</v>
@@ -8602,7 +8602,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="45" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="45" s="298">
       <c r="A45" s="57" t="inlineStr">
         <is>
           <t>L</t>
@@ -8664,7 +8664,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="46" s="298">
       <c r="A46" s="369" t="n"/>
       <c r="B46" s="8" t="n">
         <v>6</v>
@@ -8722,7 +8722,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="47" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="47" s="298">
       <c r="A47" s="57" t="inlineStr">
         <is>
           <t>M</t>
@@ -8784,7 +8784,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="48" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="48" s="298">
       <c r="A48" s="370" t="n"/>
       <c r="B48" s="8" t="n">
         <v>6</v>
@@ -8842,7 +8842,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="49" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="49" s="298">
       <c r="A49" s="370" t="n"/>
       <c r="B49" s="8" t="n">
         <v>7</v>
@@ -8900,7 +8900,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="50" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="50" s="298">
       <c r="A50" s="370" t="n"/>
       <c r="B50" s="8" t="n">
         <v>7</v>
@@ -8958,7 +8958,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="51" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="51" s="298">
       <c r="A51" s="370" t="n"/>
       <c r="B51" s="8" t="n">
         <v>6</v>
@@ -9016,7 +9016,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="52" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="52" s="298">
       <c r="A52" s="369" t="n"/>
       <c r="B52" s="8" t="n">
         <v>7</v>
@@ -9074,7 +9074,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="53" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="53" s="298">
       <c r="A53" s="57" t="inlineStr">
         <is>
           <t>N</t>
@@ -9136,7 +9136,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="54" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="54" s="298">
       <c r="A54" s="369" t="n"/>
       <c r="B54" s="8" t="n">
         <v>6</v>
@@ -9194,7 +9194,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="55" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="55" s="298">
       <c r="A55" s="57" t="inlineStr">
         <is>
           <t>O</t>
@@ -9256,7 +9256,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="56" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="56" s="298">
       <c r="A56" s="369" t="n"/>
       <c r="B56" s="8" t="n">
         <v>7</v>
@@ -9314,7 +9314,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="57" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="57" s="298">
       <c r="A57" s="57" t="inlineStr">
         <is>
           <t>P</t>
@@ -9376,7 +9376,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="58" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="58" s="298">
       <c r="A58" s="369" t="n"/>
       <c r="B58" s="8" t="n">
         <v>7</v>
@@ -9434,7 +9434,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="59" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="59" s="298">
       <c r="A59" s="59" t="inlineStr">
         <is>
           <t>Q</t>
@@ -9496,7 +9496,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="60" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="60" s="298">
       <c r="A60" s="57" t="inlineStr">
         <is>
           <t>R</t>
@@ -9558,7 +9558,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="61" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="61" s="298">
       <c r="A61" s="370" t="n"/>
       <c r="B61" s="8" t="n">
         <v>6</v>
@@ -9616,7 +9616,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="62" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="62" s="298">
       <c r="A62" s="369" t="n"/>
       <c r="B62" s="46" t="n">
         <v>7</v>
@@ -9674,7 +9674,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="63" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="63" s="298">
       <c r="A63" s="57" t="inlineStr">
         <is>
           <t>S</t>
@@ -9736,7 +9736,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="64" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="64" s="298">
       <c r="A64" s="370" t="n"/>
       <c r="B64" s="8" t="n">
         <v>7</v>
@@ -9794,7 +9794,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="65" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="65" s="298">
       <c r="A65" s="370" t="n"/>
       <c r="B65" s="8" t="n">
         <v>7</v>
@@ -9852,7 +9852,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="66" ht="94.5" customHeight="1" s="298">
+    <row customHeight="1" ht="94.5" r="66" s="298">
       <c r="A66" s="369" t="n"/>
       <c r="B66" s="8" t="n">
         <v>6</v>
@@ -9920,7 +9920,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="67" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="67" s="298">
       <c r="A67" s="57" t="inlineStr">
         <is>
           <t>T</t>
@@ -9982,7 +9982,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="68" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="68" s="298">
       <c r="A68" s="370" t="n"/>
       <c r="B68" s="8" t="n">
         <v>6</v>
@@ -10040,7 +10040,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="69" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="69" s="298">
       <c r="A69" s="370" t="n"/>
       <c r="B69" s="8" t="n">
         <v>6</v>
@@ -10098,7 +10098,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="70" ht="94.5" customHeight="1" s="298">
+    <row customHeight="1" ht="94.5" r="70" s="298">
       <c r="A70" s="370" t="n"/>
       <c r="B70" s="8" t="n">
         <v>6</v>
@@ -10166,7 +10166,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="71" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="71" s="298">
       <c r="A71" s="370" t="n"/>
       <c r="B71" s="8" t="n">
         <v>7</v>
@@ -10224,7 +10224,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="72" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="72" s="298">
       <c r="A72" s="369" t="n"/>
       <c r="B72" s="8" t="n">
         <v>7</v>
@@ -10282,7 +10282,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="73" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="73" s="298">
       <c r="A73" s="57" t="inlineStr">
         <is>
           <t>U</t>
@@ -10344,7 +10344,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="74" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="74" s="298">
       <c r="A74" s="57" t="inlineStr">
         <is>
           <t>W</t>
@@ -10406,7 +10406,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="75" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="75" s="298">
       <c r="A75" s="370" t="n"/>
       <c r="B75" s="8" t="n">
         <v>6</v>
@@ -10464,7 +10464,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="76" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="76" s="298">
       <c r="A76" s="370" t="n"/>
       <c r="B76" s="8" t="n">
         <v>6</v>
@@ -10522,7 +10522,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="77" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="77" s="298">
       <c r="A77" s="370" t="n"/>
       <c r="B77" s="8" t="n">
         <v>6</v>
@@ -10580,7 +10580,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="78" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="78" s="298">
       <c r="A78" s="370" t="n"/>
       <c r="B78" s="8" t="n">
         <v>7</v>
@@ -10638,7 +10638,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="79" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="79" s="298">
       <c r="A79" s="370" t="n"/>
       <c r="B79" s="8" t="n">
         <v>6</v>
@@ -10696,7 +10696,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="80" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="80" s="298">
       <c r="A80" s="370" t="n"/>
       <c r="B80" s="8" t="n">
         <v>7</v>
@@ -10754,7 +10754,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="81" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="81" s="298">
       <c r="A81" s="370" t="n"/>
       <c r="B81" s="8" t="n">
         <v>6</v>
@@ -10812,7 +10812,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="82" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="82" s="298">
       <c r="A82" s="370" t="n"/>
       <c r="B82" s="46" t="n">
         <v>6</v>
@@ -10870,7 +10870,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="83" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="83" s="298">
       <c r="A83" s="370" t="n"/>
       <c r="B83" s="8" t="n">
         <v>7</v>
@@ -10928,7 +10928,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="84" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="84" s="298">
       <c r="A84" s="369" t="n"/>
       <c r="B84" s="8" t="n">
         <v>7</v>
@@ -10986,7 +10986,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="85" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="85" s="298">
       <c r="A85" s="57" t="inlineStr">
         <is>
           <t>X</t>
@@ -11048,7 +11048,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="86" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="86" s="298">
       <c r="A86" s="370" t="n"/>
       <c r="B86" s="8" t="n">
         <v>6</v>
@@ -11106,7 +11106,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="87" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="87" s="298">
       <c r="A87" s="370" t="n"/>
       <c r="B87" s="8" t="n">
         <v>6</v>
@@ -11164,7 +11164,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="88" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="88" s="298">
       <c r="A88" s="370" t="n"/>
       <c r="B88" s="8" t="n">
         <v>6</v>
@@ -11222,7 +11222,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="89" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="89" s="298">
       <c r="A89" s="370" t="n"/>
       <c r="B89" s="8" t="n">
         <v>7</v>
@@ -11280,7 +11280,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="90" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="90" s="298">
       <c r="A90" s="370" t="n"/>
       <c r="B90" s="8" t="n">
         <v>6</v>
@@ -11338,7 +11338,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="91" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="91" s="298">
       <c r="A91" s="370" t="n"/>
       <c r="B91" s="8" t="n">
         <v>6</v>
@@ -11396,7 +11396,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="92" s="298">
       <c r="A92" s="370" t="n"/>
       <c r="B92" s="8" t="n">
         <v>6</v>
@@ -11454,7 +11454,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="93" s="298">
       <c r="A93" s="369" t="n"/>
       <c r="B93" s="8" t="n">
         <v>6</v>
@@ -11512,7 +11512,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="94" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="94" s="298">
       <c r="A94" s="57" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11574,7 +11574,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="95" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="95" s="298">
       <c r="A95" s="369" t="n"/>
       <c r="B95" s="8" t="n">
         <v>7</v>
@@ -11632,7 +11632,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="96" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="96" s="298">
       <c r="A96" s="57" t="inlineStr">
         <is>
           <t>Z</t>
@@ -11694,7 +11694,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="97" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="97" s="298">
       <c r="A97" s="370" t="n"/>
       <c r="B97" s="8" t="n">
         <v>6</v>
@@ -11752,7 +11752,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="98" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="98" s="298">
       <c r="A98" s="370" t="n"/>
       <c r="B98" s="8" t="n">
         <v>6</v>
@@ -11810,7 +11810,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="99" s="298">
       <c r="A99" s="370" t="n"/>
       <c r="B99" s="8" t="n">
         <v>6</v>
@@ -11868,7 +11868,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="100" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="100" s="298">
       <c r="A100" s="370" t="n"/>
       <c r="B100" s="8" t="n">
         <v>7</v>
@@ -11926,7 +11926,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="101" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="101" s="298">
       <c r="A101" s="369" t="n"/>
       <c r="B101" s="8" t="n">
         <v>7</v>
@@ -11985,7 +11985,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection autoFilter="1" deleteColumns="1" deleteRows="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertHyperlinks="1" insertRows="1" objects="1" pivotTables="1" scenarios="0" selectLockedCells="0" selectUnlockedCells="0" sheet="1" sort="1"/>
   <mergeCells count="21">
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A16"/>
@@ -12010,11 +12010,11 @@
     <mergeCell ref="A96:A101"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:M101">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule dxfId="0" priority="1" type="expression">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -12028,19 +12028,19 @@
   <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.641666666666669" defaultRowHeight="14.25"/>
   <cols>
-    <col width="8.725" customWidth="1" style="1" min="1" max="2"/>
-    <col width="20.6333333333333" customWidth="1" style="1" min="3" max="3"/>
-    <col width="8.725" customWidth="1" style="1" min="4" max="4"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="5" max="5"/>
-    <col width="8.725" customWidth="1" style="1" min="6" max="6"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9.175000000000001" customWidth="1" style="1" min="8" max="8"/>
-    <col width="8.725" customWidth="1" style="2" min="9" max="10"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="11" max="11"/>
-    <col width="8.725" customWidth="1" style="1" min="12" max="256"/>
+    <col customWidth="1" max="2" min="1" style="1" width="8.725"/>
+    <col customWidth="1" max="3" min="3" style="1" width="20.6333333333333"/>
+    <col customWidth="1" max="4" min="4" style="1" width="8.725"/>
+    <col customWidth="1" max="5" min="5" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="6" min="6" style="1" width="8.725"/>
+    <col customWidth="1" max="7" min="7" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="8" min="8" style="1" width="9.175000000000001"/>
+    <col customWidth="1" max="10" min="9" style="2" width="8.725"/>
+    <col customWidth="1" max="11" min="11" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="256" min="12" style="1" width="8.725"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" customHeight="1" s="298">
+    <row customHeight="1" ht="40.5" r="1" s="298">
       <c r="A1" s="36" t="inlineStr">
         <is>
           <t>音序</t>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="2" s="298">
       <c r="A2" s="57" t="inlineStr">
         <is>
           <t>*</t>
@@ -12170,7 +12170,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="3" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="3" s="298">
       <c r="A3" s="370" t="n"/>
       <c r="B3" s="8" t="n">
         <v>10</v>
@@ -12228,7 +12228,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="4" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="4" s="298">
       <c r="A4" s="370" t="n"/>
       <c r="B4" s="8" t="n">
         <v>10</v>
@@ -12286,7 +12286,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="5" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="5" s="298">
       <c r="A5" s="370" t="n"/>
       <c r="B5" s="8" t="n">
         <v>9</v>
@@ -12344,7 +12344,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="6" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="6" s="298">
       <c r="A6" s="369" t="n"/>
       <c r="B6" s="8" t="n">
         <v>9</v>
@@ -12402,7 +12402,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="7" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="7" s="298">
       <c r="A7" s="59" t="inlineStr">
         <is>
           <t>A</t>
@@ -12464,7 +12464,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="8" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="8" s="298">
       <c r="A8" s="370" t="n"/>
       <c r="B8" s="8" t="n">
         <v>9</v>
@@ -12522,7 +12522,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="9" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="9" s="298">
       <c r="A9" s="369" t="n"/>
       <c r="B9" s="8" t="n">
         <v>10</v>
@@ -12580,7 +12580,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="10" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="10" s="298">
       <c r="A10" s="57" t="inlineStr">
         <is>
           <t>B</t>
@@ -12642,7 +12642,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="11" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="11" s="298">
       <c r="A11" s="370" t="n"/>
       <c r="B11" s="8" t="n">
         <v>8</v>
@@ -12700,7 +12700,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="12" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="12" s="298">
       <c r="A12" s="370" t="n"/>
       <c r="B12" s="8" t="n">
         <v>9</v>
@@ -12758,7 +12758,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="13" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="13" s="298">
       <c r="A13" s="370" t="n"/>
       <c r="B13" s="8" t="n">
         <v>9</v>
@@ -12816,7 +12816,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="14" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="14" s="298">
       <c r="A14" s="370" t="n"/>
       <c r="B14" s="8" t="n">
         <v>8</v>
@@ -12874,7 +12874,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="15" s="298">
       <c r="A15" s="370" t="n"/>
       <c r="B15" s="8" t="n">
         <v>9</v>
@@ -12932,7 +12932,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="16" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="16" s="298">
       <c r="A16" s="370" t="n"/>
       <c r="B16" s="8" t="n">
         <v>8</v>
@@ -12990,7 +12990,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="17" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="17" s="298">
       <c r="A17" s="370" t="n"/>
       <c r="B17" s="8" t="n">
         <v>9</v>
@@ -13048,7 +13048,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="18" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="18" s="298">
       <c r="A18" s="369" t="n"/>
       <c r="B18" s="8" t="n">
         <v>9</v>
@@ -13106,7 +13106,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="19" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="19" s="298">
       <c r="A19" s="57" t="inlineStr">
         <is>
           <t>C</t>
@@ -13168,7 +13168,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="20" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="20" s="298">
       <c r="A20" s="370" t="n"/>
       <c r="B20" s="8" t="n">
         <v>9</v>
@@ -13226,7 +13226,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="21" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="21" s="298">
       <c r="A21" s="370" t="n"/>
       <c r="B21" s="8" t="n">
         <v>10</v>
@@ -13284,7 +13284,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="22" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="22" s="298">
       <c r="A22" s="370" t="n"/>
       <c r="B22" s="8" t="n">
         <v>9</v>
@@ -13342,7 +13342,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="23" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="23" s="298">
       <c r="A23" s="370" t="n"/>
       <c r="B23" s="8" t="n">
         <v>10</v>
@@ -13400,7 +13400,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="24" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="24" s="298">
       <c r="A24" s="369" t="n"/>
       <c r="B24" s="8" t="n">
         <v>10</v>
@@ -13458,7 +13458,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="25" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="25" s="298">
       <c r="A25" s="57" t="inlineStr">
         <is>
           <t>D</t>
@@ -13520,7 +13520,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="26" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="26" s="298">
       <c r="A26" s="370" t="n"/>
       <c r="B26" s="8" t="n">
         <v>10</v>
@@ -13578,7 +13578,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="27" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="27" s="298">
       <c r="A27" s="370" t="n"/>
       <c r="B27" s="8" t="n">
         <v>10</v>
@@ -13636,7 +13636,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="28" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="28" s="298">
       <c r="A28" s="369" t="n"/>
       <c r="B28" s="8" t="n">
         <v>9</v>
@@ -13694,7 +13694,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="29" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="29" s="298">
       <c r="A29" s="57" t="inlineStr">
         <is>
           <t>F</t>
@@ -13756,7 +13756,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="30" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="30" s="298">
       <c r="A30" s="370" t="n"/>
       <c r="B30" s="8" t="n">
         <v>9</v>
@@ -13814,7 +13814,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="31" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="31" s="298">
       <c r="A31" s="370" t="n"/>
       <c r="B31" s="8" t="n">
         <v>9</v>
@@ -13872,7 +13872,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="32" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="32" s="298">
       <c r="A32" s="370" t="n"/>
       <c r="B32" s="8" t="n">
         <v>10</v>
@@ -13930,7 +13930,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="33" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="33" s="298">
       <c r="A33" s="370" t="n"/>
       <c r="B33" s="46" t="n">
         <v>8</v>
@@ -13988,7 +13988,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="34" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="34" s="298">
       <c r="A34" s="370" t="n"/>
       <c r="B34" s="8" t="n">
         <v>9</v>
@@ -14046,7 +14046,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="35" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="35" s="298">
       <c r="A35" s="369" t="n"/>
       <c r="B35" s="8" t="n">
         <v>8</v>
@@ -14104,7 +14104,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="36" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="36" s="298">
       <c r="A36" s="57" t="inlineStr">
         <is>
           <t>G</t>
@@ -14166,7 +14166,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="37" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="37" s="298">
       <c r="A37" s="370" t="n"/>
       <c r="B37" s="46" t="n">
         <v>9</v>
@@ -14224,7 +14224,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="38" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="38" s="298">
       <c r="A38" s="370" t="n"/>
       <c r="B38" s="8" t="n">
         <v>9</v>
@@ -14282,7 +14282,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="39" ht="110.25" customHeight="1" s="298">
+    <row customHeight="1" ht="110.25" r="39" s="298">
       <c r="A39" s="370" t="n"/>
       <c r="B39" s="8" t="n">
         <v>10</v>
@@ -14349,7 +14349,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="40" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="40" s="298">
       <c r="A40" s="370" t="n"/>
       <c r="B40" s="8" t="n">
         <v>10</v>
@@ -14407,7 +14407,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="41" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="41" s="298">
       <c r="A41" s="369" t="n"/>
       <c r="B41" s="8" t="n">
         <v>8</v>
@@ -14465,7 +14465,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="42" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="42" s="298">
       <c r="A42" s="57" t="inlineStr">
         <is>
           <t>H</t>
@@ -14527,7 +14527,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="43" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="43" s="298">
       <c r="A43" s="370" t="n"/>
       <c r="B43" s="8" t="n">
         <v>9</v>
@@ -14585,7 +14585,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="44" ht="36" customHeight="1" s="298">
+    <row customHeight="1" ht="36" r="44" s="298">
       <c r="A44" s="370" t="n"/>
       <c r="B44" s="8" t="n">
         <v>9</v>
@@ -14643,7 +14643,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="45" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="45" s="298">
       <c r="A45" s="370" t="n"/>
       <c r="B45" s="8" t="n">
         <v>8</v>
@@ -14701,7 +14701,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="46" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="46" s="298">
       <c r="A46" s="370" t="n"/>
       <c r="B46" s="46" t="n">
         <v>9</v>
@@ -14759,7 +14759,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="47" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="47" s="298">
       <c r="A47" s="369" t="n"/>
       <c r="B47" s="46" t="n">
         <v>8</v>
@@ -14817,7 +14817,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="48" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="48" s="298">
       <c r="A48" s="57" t="inlineStr">
         <is>
           <t>I</t>
@@ -14879,7 +14879,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="49" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="49" s="298">
       <c r="A49" s="369" t="n"/>
       <c r="B49" s="8" t="n">
         <v>8</v>
@@ -14937,7 +14937,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="50" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="50" s="298">
       <c r="A50" s="57" t="inlineStr">
         <is>
           <t>J</t>
@@ -14999,7 +14999,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="51" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="51" s="298">
       <c r="A51" s="370" t="n"/>
       <c r="B51" s="8" t="n">
         <v>10</v>
@@ -15057,7 +15057,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="52" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="52" s="298">
       <c r="A52" s="370" t="n"/>
       <c r="B52" s="8" t="n">
         <v>9</v>
@@ -15115,7 +15115,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="53" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="53" s="298">
       <c r="A53" s="370" t="n"/>
       <c r="B53" s="8" t="n">
         <v>8</v>
@@ -15173,7 +15173,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="54" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="54" s="298">
       <c r="A54" s="369" t="n"/>
       <c r="B54" s="8" t="n">
         <v>10</v>
@@ -15231,7 +15231,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="55" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="55" s="298">
       <c r="A55" s="57" t="inlineStr">
         <is>
           <t>K</t>
@@ -15293,7 +15293,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="56" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="56" s="298">
       <c r="A56" s="370" t="n"/>
       <c r="B56" s="8" t="n">
         <v>9</v>
@@ -15351,7 +15351,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="57" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="57" s="298">
       <c r="A57" s="370" t="n"/>
       <c r="B57" s="8" t="n">
         <v>10</v>
@@ -15409,7 +15409,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="58" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="58" s="298">
       <c r="A58" s="369" t="n"/>
       <c r="B58" s="8" t="n">
         <v>10</v>
@@ -15467,7 +15467,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="59" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="59" s="298">
       <c r="A59" s="57" t="inlineStr">
         <is>
           <t>L</t>
@@ -15529,7 +15529,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="60" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="60" s="298">
       <c r="A60" s="370" t="n"/>
       <c r="B60" s="8" t="n">
         <v>10</v>
@@ -15587,7 +15587,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="61" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="61" s="298">
       <c r="A61" s="370" t="n"/>
       <c r="B61" s="8" t="n">
         <v>8</v>
@@ -15645,7 +15645,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="62" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="62" s="298">
       <c r="A62" s="370" t="n"/>
       <c r="B62" s="8" t="n">
         <v>8</v>
@@ -15703,7 +15703,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="63" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="63" s="298">
       <c r="A63" s="370" t="n"/>
       <c r="B63" s="8" t="n">
         <v>9</v>
@@ -15761,7 +15761,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="64" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="64" s="298">
       <c r="A64" s="370" t="n"/>
       <c r="B64" s="8" t="n">
         <v>8</v>
@@ -15819,7 +15819,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="65" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="65" s="298">
       <c r="A65" s="370" t="n"/>
       <c r="B65" s="8" t="n">
         <v>10</v>
@@ -15877,7 +15877,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="66" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="66" s="298">
       <c r="A66" s="369" t="n"/>
       <c r="B66" s="8" t="n">
         <v>9</v>
@@ -15935,7 +15935,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="67" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="67" s="298">
       <c r="A67" s="57" t="inlineStr">
         <is>
           <t>M</t>
@@ -15999,7 +15999,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="68" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="68" s="298">
       <c r="A68" s="369" t="n"/>
       <c r="B68" s="8" t="n">
         <v>10</v>
@@ -16057,7 +16057,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="69" s="298">
       <c r="A69" s="57" t="inlineStr">
         <is>
           <t>N</t>
@@ -16119,7 +16119,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="70" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="70" s="298">
       <c r="A70" s="370" t="n"/>
       <c r="B70" s="8" t="n">
         <v>9</v>
@@ -16177,7 +16177,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="71" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="71" s="298">
       <c r="A71" s="370" t="n"/>
       <c r="B71" s="8" t="n">
         <v>9</v>
@@ -16235,7 +16235,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="72" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="72" s="298">
       <c r="A72" s="369" t="n"/>
       <c r="B72" s="8" t="n">
         <v>9</v>
@@ -16293,7 +16293,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="73" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="73" s="298">
       <c r="A73" s="51" t="inlineStr">
         <is>
           <t>O</t>
@@ -16355,7 +16355,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" ht="126" customHeight="1" s="298">
+    <row customHeight="1" ht="126" r="74" s="298">
       <c r="A74" s="51" t="inlineStr">
         <is>
           <t>P</t>
@@ -16427,7 +16427,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="75" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="75" s="298">
       <c r="A75" s="370" t="n"/>
       <c r="B75" s="8" t="n">
         <v>10</v>
@@ -16485,7 +16485,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="76" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="76" s="298">
       <c r="A76" s="370" t="n"/>
       <c r="B76" s="8" t="n">
         <v>10</v>
@@ -16543,7 +16543,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="77" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="77" s="298">
       <c r="A77" s="370" t="n"/>
       <c r="B77" s="46" t="n">
         <v>9</v>
@@ -16601,7 +16601,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="78" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="78" s="298">
       <c r="A78" s="369" t="n"/>
       <c r="B78" s="8" t="n">
         <v>8</v>
@@ -16659,7 +16659,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="79" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="79" s="298">
       <c r="A79" s="57" t="inlineStr">
         <is>
           <t>Q</t>
@@ -16721,7 +16721,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="80" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="80" s="298">
       <c r="A80" s="370" t="n"/>
       <c r="B80" s="8" t="n">
         <v>8</v>
@@ -16779,7 +16779,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="81" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="81" s="298">
       <c r="A81" s="370" t="n"/>
       <c r="B81" s="8" t="n">
         <v>8</v>
@@ -16837,7 +16837,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="82" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="82" s="298">
       <c r="A82" s="370" t="n"/>
       <c r="B82" s="8" t="n">
         <v>9</v>
@@ -16895,7 +16895,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="83" ht="126" customHeight="1" s="298">
+    <row customHeight="1" ht="126" r="83" s="298">
       <c r="A83" s="369" t="n"/>
       <c r="B83" s="8" t="n">
         <v>9</v>
@@ -16963,7 +16963,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="84" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="84" s="298">
       <c r="A84" s="57" t="inlineStr">
         <is>
           <t>R</t>
@@ -17025,7 +17025,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="85" ht="94.5" customHeight="1" s="298">
+    <row customHeight="1" ht="94.5" r="85" s="298">
       <c r="A85" s="370" t="n"/>
       <c r="B85" s="8" t="n">
         <v>8</v>
@@ -17093,7 +17093,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="86" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="86" s="298">
       <c r="A86" s="370" t="n"/>
       <c r="B86" s="8" t="n">
         <v>9</v>
@@ -17151,7 +17151,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="87" ht="157.5" customHeight="1" s="298">
+    <row customHeight="1" ht="157.5" r="87" s="298">
       <c r="A87" s="369" t="n"/>
       <c r="B87" s="8" t="n">
         <v>8</v>
@@ -17219,7 +17219,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="88" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="88" s="298">
       <c r="A88" s="57" t="inlineStr">
         <is>
           <t>S</t>
@@ -17281,7 +17281,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="89" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="89" s="298">
       <c r="A89" s="370" t="n"/>
       <c r="B89" s="8" t="n">
         <v>9</v>
@@ -17339,7 +17339,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="90" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="90" s="298">
       <c r="A90" s="370" t="n"/>
       <c r="B90" s="8" t="n">
         <v>8</v>
@@ -17397,7 +17397,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="91" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="91" s="298">
       <c r="A91" s="370" t="n"/>
       <c r="B91" s="8" t="n">
         <v>9</v>
@@ -17455,7 +17455,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="92" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="92" s="298">
       <c r="A92" s="370" t="n"/>
       <c r="B92" s="8" t="n">
         <v>10</v>
@@ -17513,7 +17513,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="93" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="93" s="298">
       <c r="A93" s="370" t="n"/>
       <c r="B93" s="8" t="n">
         <v>9</v>
@@ -17571,7 +17571,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="94" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="94" s="298">
       <c r="A94" s="370" t="n"/>
       <c r="B94" s="8" t="n">
         <v>9</v>
@@ -17629,7 +17629,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="95" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="95" s="298">
       <c r="A95" s="369" t="n"/>
       <c r="B95" s="8" t="n">
         <v>10</v>
@@ -17687,7 +17687,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="96" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="96" s="298">
       <c r="A96" s="51" t="inlineStr">
         <is>
           <t>T</t>
@@ -17749,7 +17749,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="97" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="97" s="298">
       <c r="A97" s="370" t="n"/>
       <c r="B97" s="8" t="n">
         <v>10</v>
@@ -17807,7 +17807,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="98" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="98" s="298">
       <c r="A98" s="370" t="n"/>
       <c r="B98" s="8" t="n">
         <v>8</v>
@@ -17865,7 +17865,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="99" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="99" s="298">
       <c r="A99" s="370" t="n"/>
       <c r="B99" s="8" t="n">
         <v>8</v>
@@ -17923,7 +17923,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="100" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="100" s="298">
       <c r="A100" s="369" t="n"/>
       <c r="B100" s="46" t="n">
         <v>8</v>
@@ -17981,7 +17981,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="101" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="101" s="298">
       <c r="A101" s="57" t="inlineStr">
         <is>
           <t>V</t>
@@ -18043,7 +18043,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="102" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="102" s="298">
       <c r="A102" s="369" t="n"/>
       <c r="B102" s="8" t="n">
         <v>10</v>
@@ -18101,7 +18101,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="103" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="103" s="298">
       <c r="A103" s="57" t="inlineStr">
         <is>
           <t>W</t>
@@ -18163,7 +18163,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="104" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="104" s="298">
       <c r="A104" s="370" t="n"/>
       <c r="B104" s="8" t="n">
         <v>9</v>
@@ -18221,7 +18221,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="105" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="105" s="298">
       <c r="A105" s="370" t="n"/>
       <c r="B105" s="8" t="n">
         <v>9</v>
@@ -18279,7 +18279,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="106" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="106" s="298">
       <c r="A106" s="370" t="n"/>
       <c r="B106" s="8" t="n">
         <v>8</v>
@@ -18337,7 +18337,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="107" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="107" s="298">
       <c r="A107" s="370" t="n"/>
       <c r="B107" s="46" t="n">
         <v>8</v>
@@ -18395,7 +18395,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="108" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="108" s="298">
       <c r="A108" s="370" t="n"/>
       <c r="B108" s="46" t="n">
         <v>9</v>
@@ -18453,7 +18453,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="109" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="109" s="298">
       <c r="A109" s="370" t="n"/>
       <c r="B109" s="8" t="n">
         <v>9</v>
@@ -18511,7 +18511,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="110" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="110" s="298">
       <c r="A110" s="370" t="n"/>
       <c r="B110" s="46" t="n">
         <v>9</v>
@@ -18569,7 +18569,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="111" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="111" s="298">
       <c r="A111" s="370" t="n"/>
       <c r="B111" s="8" t="n">
         <v>10</v>
@@ -18627,7 +18627,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="112" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="112" s="298">
       <c r="A112" s="369" t="n"/>
       <c r="B112" s="46" t="n">
         <v>8</v>
@@ -18685,7 +18685,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="113" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="113" s="298">
       <c r="A113" s="57" t="inlineStr">
         <is>
           <t>X</t>
@@ -18747,7 +18747,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="114" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="114" s="298">
       <c r="A114" s="369" t="n"/>
       <c r="B114" s="8" t="n">
         <v>8</v>
@@ -18805,7 +18805,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="115" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="115" s="298">
       <c r="A115" s="57" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18867,7 +18867,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="116" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="116" s="298">
       <c r="A116" s="370" t="n"/>
       <c r="B116" s="8" t="n">
         <v>10</v>
@@ -18925,7 +18925,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="117" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="117" s="298">
       <c r="A117" s="370" t="n"/>
       <c r="B117" s="46" t="n">
         <v>10</v>
@@ -18983,7 +18983,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="118" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="118" s="298">
       <c r="A118" s="370" t="n"/>
       <c r="B118" s="8" t="n">
         <v>9</v>
@@ -19041,7 +19041,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="119" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="119" s="298">
       <c r="A119" s="370" t="n"/>
       <c r="B119" s="8" t="n">
         <v>10</v>
@@ -19099,7 +19099,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="120" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="120" s="298">
       <c r="A120" s="369" t="n"/>
       <c r="B120" s="8" t="n">
         <v>9</v>
@@ -19157,7 +19157,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="121" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="121" s="298">
       <c r="A121" s="57" t="inlineStr">
         <is>
           <t>Z</t>
@@ -19219,7 +19219,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="122" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="122" s="298">
       <c r="A122" s="370" t="n"/>
       <c r="B122" s="8" t="n">
         <v>10</v>
@@ -19277,7 +19277,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="123" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="123" s="298">
       <c r="A123" s="370" t="n"/>
       <c r="B123" s="8" t="n">
         <v>10</v>
@@ -19335,7 +19335,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="124" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="124" s="298">
       <c r="A124" s="369" t="n"/>
       <c r="B124" s="8" t="n">
         <v>9</v>
@@ -19394,7 +19394,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection autoFilter="1" deleteColumns="1" deleteRows="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertHyperlinks="1" insertRows="1" objects="1" pivotTables="1" scenarios="0" selectLockedCells="0" selectUnlockedCells="0" sheet="1" sort="1"/>
   <mergeCells count="24">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A9"/>
@@ -19422,11 +19422,11 @@
     <mergeCell ref="A121:A124"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:M124">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule dxfId="0" priority="1" type="expression">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -19440,19 +19440,19 @@
   <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.641666666666669" defaultRowHeight="14.25"/>
   <cols>
-    <col width="8.725" customWidth="1" style="1" min="1" max="2"/>
-    <col width="20.6333333333333" customWidth="1" style="1" min="3" max="3"/>
-    <col width="8.725" customWidth="1" style="1" min="4" max="4"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="5" max="5"/>
-    <col width="8.725" customWidth="1" style="1" min="6" max="6"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9.08333333333333" customWidth="1" style="1" min="8" max="8"/>
-    <col width="8.725" customWidth="1" style="2" min="9" max="10"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="11" max="11"/>
-    <col width="8.725" customWidth="1" style="1" min="12" max="256"/>
+    <col customWidth="1" max="2" min="1" style="1" width="8.725"/>
+    <col customWidth="1" max="3" min="3" style="1" width="20.6333333333333"/>
+    <col customWidth="1" max="4" min="4" style="1" width="8.725"/>
+    <col customWidth="1" max="5" min="5" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="6" min="6" style="1" width="8.725"/>
+    <col customWidth="1" max="7" min="7" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="8" min="8" style="1" width="9.08333333333333"/>
+    <col customWidth="1" max="10" min="9" style="2" width="8.725"/>
+    <col customWidth="1" max="11" min="11" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="256" min="12" style="1" width="8.725"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" customHeight="1" s="298">
+    <row customHeight="1" ht="40.5" r="1" s="298">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>音序</t>
@@ -19520,7 +19520,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="2" s="298">
       <c r="A2" s="20" t="inlineStr">
         <is>
           <t>*</t>
@@ -19582,7 +19582,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="3" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="3" s="298">
       <c r="A3" s="20" t="inlineStr">
         <is>
           <t>A</t>
@@ -19644,7 +19644,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="4" s="298">
       <c r="A4" s="369" t="n"/>
       <c r="B4" s="8" t="n">
         <v>6</v>
@@ -19702,7 +19702,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="5" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="5" s="298">
       <c r="A5" s="20" t="inlineStr">
         <is>
           <t>B</t>
@@ -19764,7 +19764,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="6" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="6" s="298">
       <c r="A6" s="370" t="n"/>
       <c r="B6" s="8" t="n">
         <v>7</v>
@@ -19822,7 +19822,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="7" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="7" s="298">
       <c r="A7" s="370" t="n"/>
       <c r="B7" s="8" t="n">
         <v>6</v>
@@ -19880,7 +19880,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="8" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="8" s="298">
       <c r="A8" s="370" t="n"/>
       <c r="B8" s="8" t="n">
         <v>6</v>
@@ -19938,7 +19938,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="9" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="9" s="298">
       <c r="A9" s="370" t="n"/>
       <c r="B9" s="8" t="n">
         <v>6</v>
@@ -19996,7 +19996,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="10" s="298">
       <c r="A10" s="370" t="n"/>
       <c r="B10" s="8" t="n">
         <v>6</v>
@@ -20054,7 +20054,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="11" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="11" s="298">
       <c r="A11" s="370" t="n"/>
       <c r="B11" s="8" t="n">
         <v>7</v>
@@ -20112,7 +20112,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="12" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="12" s="298">
       <c r="A12" s="370" t="n"/>
       <c r="B12" s="8" t="n">
         <v>6</v>
@@ -20170,7 +20170,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="13" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="13" s="298">
       <c r="A13" s="370" t="n"/>
       <c r="B13" s="8" t="n">
         <v>6</v>
@@ -20228,7 +20228,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="14" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="14" s="298">
       <c r="A14" s="369" t="n"/>
       <c r="B14" s="8" t="n">
         <v>7</v>
@@ -20286,7 +20286,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="15" s="298">
       <c r="A15" s="20" t="inlineStr">
         <is>
           <t>C</t>
@@ -20348,7 +20348,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="16" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="16" s="298">
       <c r="A16" s="369" t="n"/>
       <c r="B16" s="8" t="n">
         <v>7</v>
@@ -20406,7 +20406,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="17" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="17" s="298">
       <c r="A17" s="35" t="inlineStr">
         <is>
           <t>D</t>
@@ -20468,7 +20468,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="18" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="18" s="298">
       <c r="A18" s="370" t="n"/>
       <c r="B18" s="8" t="n">
         <v>6</v>
@@ -20526,7 +20526,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="19" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="19" s="298">
       <c r="A19" s="369" t="n"/>
       <c r="B19" s="8" t="n">
         <v>7</v>
@@ -20584,7 +20584,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="20" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="20" s="298">
       <c r="A20" s="35" t="inlineStr">
         <is>
           <t>F</t>
@@ -20646,7 +20646,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="21" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="21" s="298">
       <c r="A21" s="370" t="n"/>
       <c r="B21" s="8" t="n">
         <v>6</v>
@@ -20704,7 +20704,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="22" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="22" s="298">
       <c r="A22" s="369" t="n"/>
       <c r="B22" s="8" t="n">
         <v>7</v>
@@ -20762,7 +20762,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="23" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="23" s="298">
       <c r="A23" s="35" t="inlineStr">
         <is>
           <t>G</t>
@@ -20824,7 +20824,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="24" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="24" s="298">
       <c r="A24" s="370" t="n"/>
       <c r="B24" s="8" t="n">
         <v>7</v>
@@ -20882,7 +20882,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="25" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="25" s="298">
       <c r="A25" s="370" t="n"/>
       <c r="B25" s="8" t="n">
         <v>6</v>
@@ -20940,7 +20940,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="26" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="26" s="298">
       <c r="A26" s="370" t="n"/>
       <c r="B26" s="8" t="n">
         <v>6</v>
@@ -20998,7 +20998,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="27" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="27" s="298">
       <c r="A27" s="370" t="n"/>
       <c r="B27" s="8" t="n">
         <v>6</v>
@@ -21056,7 +21056,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="28" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="28" s="298">
       <c r="A28" s="370" t="n"/>
       <c r="B28" s="8" t="n">
         <v>7</v>
@@ -21114,7 +21114,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="29" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="29" s="298">
       <c r="A29" s="369" t="n"/>
       <c r="B29" s="8" t="n">
         <v>6</v>
@@ -21172,7 +21172,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="30" s="298">
       <c r="A30" s="35" t="inlineStr">
         <is>
           <t>H</t>
@@ -21234,7 +21234,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="31" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="31" s="298">
       <c r="A31" s="370" t="n"/>
       <c r="B31" s="8" t="n">
         <v>6</v>
@@ -21292,7 +21292,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="32" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="32" s="298">
       <c r="A32" s="370" t="n"/>
       <c r="B32" s="8" t="n">
         <v>6</v>
@@ -21350,7 +21350,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="33" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="33" s="298">
       <c r="A33" s="370" t="n"/>
       <c r="B33" s="8" t="n">
         <v>7</v>
@@ -21408,7 +21408,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="34" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="34" s="298">
       <c r="A34" s="370" t="n"/>
       <c r="B34" s="8" t="n">
         <v>7</v>
@@ -21466,7 +21466,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="35" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="35" s="298">
       <c r="A35" s="369" t="n"/>
       <c r="B35" s="8" t="n">
         <v>6</v>
@@ -21524,7 +21524,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="36" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="36" s="298">
       <c r="A36" s="20" t="inlineStr">
         <is>
           <t>I</t>
@@ -21586,7 +21586,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="37" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="37" s="298">
       <c r="A37" s="369" t="n"/>
       <c r="B37" s="8" t="n">
         <v>7</v>
@@ -21644,7 +21644,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="38" s="298">
       <c r="A38" s="20" t="inlineStr">
         <is>
           <t>J</t>
@@ -21706,7 +21706,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="39" ht="94.5" customHeight="1" s="298">
+    <row customHeight="1" ht="94.5" r="39" s="298">
       <c r="A39" s="370" t="n"/>
       <c r="B39" s="8" t="n">
         <v>7</v>
@@ -21773,7 +21773,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="40" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="40" s="298">
       <c r="A40" s="370" t="n"/>
       <c r="B40" s="8" t="n">
         <v>6</v>
@@ -21831,7 +21831,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="41" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="41" s="298">
       <c r="A41" s="369" t="n"/>
       <c r="B41" s="8" t="n">
         <v>6</v>
@@ -21889,7 +21889,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="42" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="42" s="298">
       <c r="A42" s="20" t="inlineStr">
         <is>
           <t>K</t>
@@ -21951,7 +21951,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="43" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="43" s="298">
       <c r="A43" s="370" t="n"/>
       <c r="B43" s="8" t="n">
         <v>6</v>
@@ -22009,7 +22009,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="44" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="44" s="298">
       <c r="A44" s="370" t="n"/>
       <c r="B44" s="8" t="n">
         <v>7</v>
@@ -22067,7 +22067,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="45" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="45" s="298">
       <c r="A45" s="369" t="n"/>
       <c r="B45" s="8" t="n">
         <v>7</v>
@@ -22125,7 +22125,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="46" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="46" s="298">
       <c r="A46" s="35" t="inlineStr">
         <is>
           <t>L</t>
@@ -22187,7 +22187,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="47" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="47" s="298">
       <c r="A47" s="370" t="n"/>
       <c r="B47" s="8" t="n">
         <v>6</v>
@@ -22245,7 +22245,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="48" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="48" s="298">
       <c r="A48" s="370" t="n"/>
       <c r="B48" s="8" t="n">
         <v>7</v>
@@ -22303,7 +22303,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="49" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="49" s="298">
       <c r="A49" s="369" t="n"/>
       <c r="B49" s="8" t="n">
         <v>6</v>
@@ -22361,7 +22361,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="50" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="50" s="298">
       <c r="A50" s="20" t="inlineStr">
         <is>
           <t>M</t>
@@ -22423,7 +22423,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="51" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="51" s="298">
       <c r="A51" s="370" t="n"/>
       <c r="B51" s="8" t="n">
         <v>6</v>
@@ -22481,7 +22481,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="52" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="52" s="298">
       <c r="A52" s="370" t="n"/>
       <c r="B52" s="8" t="n">
         <v>6</v>
@@ -22539,7 +22539,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="53" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="53" s="298">
       <c r="A53" s="370" t="n"/>
       <c r="B53" s="8" t="n">
         <v>7</v>
@@ -22597,7 +22597,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="54" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="54" s="298">
       <c r="A54" s="370" t="n"/>
       <c r="B54" s="8" t="n">
         <v>6</v>
@@ -22655,7 +22655,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="55" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="55" s="298">
       <c r="A55" s="369" t="n"/>
       <c r="B55" s="8" t="n">
         <v>6</v>
@@ -22713,7 +22713,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="56" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="56" s="298">
       <c r="A56" s="35" t="inlineStr">
         <is>
           <t>N</t>
@@ -22775,7 +22775,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="57" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="57" s="298">
       <c r="A57" s="369" t="n"/>
       <c r="B57" s="8" t="n">
         <v>6</v>
@@ -22833,7 +22833,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="58" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="58" s="298">
       <c r="A58" s="35" t="inlineStr">
         <is>
           <t>O</t>
@@ -22895,7 +22895,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="59" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="59" s="298">
       <c r="A59" s="369" t="n"/>
       <c r="B59" s="8" t="n">
         <v>7</v>
@@ -22953,7 +22953,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="60" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="60" s="298">
       <c r="A60" s="20" t="inlineStr">
         <is>
           <t>P</t>
@@ -23015,7 +23015,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="61" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="61" s="298">
       <c r="A61" s="369" t="n"/>
       <c r="B61" s="8" t="n">
         <v>7</v>
@@ -23073,7 +23073,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="62" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="62" s="298">
       <c r="A62" s="20" t="inlineStr">
         <is>
           <t>Q</t>
@@ -23135,7 +23135,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="63" s="298">
       <c r="A63" s="370" t="n"/>
       <c r="B63" s="8" t="n">
         <v>6</v>
@@ -23193,7 +23193,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="64" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="64" s="298">
       <c r="A64" s="369" t="n"/>
       <c r="B64" s="8" t="n">
         <v>6</v>
@@ -23251,7 +23251,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="65" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="65" s="298">
       <c r="A65" s="20" t="inlineStr">
         <is>
           <t>R</t>
@@ -23313,7 +23313,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="66" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="66" s="298">
       <c r="A66" s="370" t="n"/>
       <c r="B66" s="8" t="n">
         <v>7</v>
@@ -23371,7 +23371,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="67" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="67" s="298">
       <c r="A67" s="370" t="n"/>
       <c r="B67" s="8" t="n">
         <v>6</v>
@@ -23429,7 +23429,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="68" ht="44.25" customHeight="1" s="298">
+    <row customHeight="1" ht="44.25" r="68" s="298">
       <c r="A68" s="369" t="n"/>
       <c r="B68" s="8" t="n">
         <v>7</v>
@@ -23487,7 +23487,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="69" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="69" s="298">
       <c r="A69" s="20" t="inlineStr">
         <is>
           <t>S</t>
@@ -23549,7 +23549,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="70" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="70" s="298">
       <c r="A70" s="370" t="n"/>
       <c r="B70" s="8" t="n">
         <v>6</v>
@@ -23607,7 +23607,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="71" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="71" s="298">
       <c r="A71" s="370" t="n"/>
       <c r="B71" s="8" t="n">
         <v>7</v>
@@ -23665,7 +23665,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="72" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="72" s="298">
       <c r="A72" s="370" t="n"/>
       <c r="B72" s="8" t="n">
         <v>7</v>
@@ -23723,7 +23723,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="73" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="73" s="298">
       <c r="A73" s="369" t="n"/>
       <c r="B73" s="8" t="n">
         <v>6</v>
@@ -23781,7 +23781,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="74" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="74" s="298">
       <c r="A74" s="20" t="inlineStr">
         <is>
           <t>T</t>
@@ -23843,7 +23843,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="75" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="75" s="298">
       <c r="A75" s="370" t="n"/>
       <c r="B75" s="8" t="n">
         <v>6</v>
@@ -23901,7 +23901,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="76" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="76" s="298">
       <c r="A76" s="370" t="n"/>
       <c r="B76" s="8" t="n">
         <v>6</v>
@@ -23959,7 +23959,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="77" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="77" s="298">
       <c r="A77" s="370" t="n"/>
       <c r="B77" s="8" t="n">
         <v>6</v>
@@ -24017,7 +24017,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="78" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="78" s="298">
       <c r="A78" s="370" t="n"/>
       <c r="B78" s="8" t="n">
         <v>7</v>
@@ -24075,7 +24075,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="79" ht="126" customHeight="1" s="298">
+    <row customHeight="1" ht="126" r="79" s="298">
       <c r="A79" s="369" t="n"/>
       <c r="B79" s="8" t="n">
         <v>7</v>
@@ -24142,7 +24142,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="80" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="80" s="298">
       <c r="A80" s="35" t="inlineStr">
         <is>
           <t>U</t>
@@ -24204,7 +24204,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="81" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="81" s="298">
       <c r="A81" s="20" t="inlineStr">
         <is>
           <t>W</t>
@@ -24266,7 +24266,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="82" ht="36" customHeight="1" s="298">
+    <row customHeight="1" ht="36" r="82" s="298">
       <c r="A82" s="370" t="n"/>
       <c r="B82" s="8" t="n">
         <v>6</v>
@@ -24324,7 +24324,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="83" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="83" s="298">
       <c r="A83" s="370" t="n"/>
       <c r="B83" s="8" t="n">
         <v>6</v>
@@ -24382,7 +24382,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="84" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="84" s="298">
       <c r="A84" s="370" t="n"/>
       <c r="B84" s="8" t="n">
         <v>6</v>
@@ -24440,7 +24440,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="85" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="85" s="298">
       <c r="A85" s="370" t="n"/>
       <c r="B85" s="8" t="n">
         <v>7</v>
@@ -24498,7 +24498,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="86" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="86" s="298">
       <c r="A86" s="370" t="n"/>
       <c r="B86" s="8" t="n">
         <v>6</v>
@@ -24556,7 +24556,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="87" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="87" s="298">
       <c r="A87" s="370" t="n"/>
       <c r="B87" s="8" t="n">
         <v>6</v>
@@ -24614,7 +24614,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="88" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="88" s="298">
       <c r="A88" s="370" t="n"/>
       <c r="B88" s="8" t="n">
         <v>7</v>
@@ -24672,7 +24672,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="89" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="89" s="298">
       <c r="A89" s="370" t="n"/>
       <c r="B89" s="8" t="n">
         <v>7</v>
@@ -24730,7 +24730,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="90" ht="36" customHeight="1" s="298">
+    <row customHeight="1" ht="36" r="90" s="298">
       <c r="A90" s="370" t="n"/>
       <c r="B90" s="8" t="n">
         <v>6</v>
@@ -24788,7 +24788,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="91" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="91" s="298">
       <c r="A91" s="370" t="n"/>
       <c r="B91" s="8" t="n">
         <v>6</v>
@@ -24846,7 +24846,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="92" s="298">
       <c r="A92" s="370" t="n"/>
       <c r="B92" s="8" t="n">
         <v>7</v>
@@ -24904,7 +24904,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="93" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="93" s="298">
       <c r="A93" s="370" t="n"/>
       <c r="B93" s="8" t="n">
         <v>6</v>
@@ -24962,7 +24962,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="94" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="94" s="298">
       <c r="A94" s="370" t="n"/>
       <c r="B94" s="8" t="n">
         <v>6</v>
@@ -25020,7 +25020,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="95" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="95" s="298">
       <c r="A95" s="369" t="n"/>
       <c r="B95" s="8" t="n">
         <v>7</v>
@@ -25078,7 +25078,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="96" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="96" s="298">
       <c r="A96" s="20" t="inlineStr">
         <is>
           <t>X</t>
@@ -25140,7 +25140,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="97" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="97" s="298">
       <c r="A97" s="370" t="n"/>
       <c r="B97" s="8" t="n">
         <v>6</v>
@@ -25198,7 +25198,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="98" s="298">
       <c r="A98" s="370" t="n"/>
       <c r="B98" s="8" t="n">
         <v>6</v>
@@ -25256,7 +25256,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="99" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="99" s="298">
       <c r="A99" s="370" t="n"/>
       <c r="B99" s="8" t="n">
         <v>7</v>
@@ -25314,7 +25314,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="100" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="100" s="298">
       <c r="A100" s="370" t="n"/>
       <c r="B100" s="8" t="n">
         <v>6</v>
@@ -25372,7 +25372,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="101" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="101" s="298">
       <c r="A101" s="370" t="n"/>
       <c r="B101" s="8" t="n">
         <v>6</v>
@@ -25430,7 +25430,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="102" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="102" s="298">
       <c r="A102" s="370" t="n"/>
       <c r="B102" s="8" t="n">
         <v>6</v>
@@ -25488,7 +25488,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="103" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="103" s="298">
       <c r="A103" s="369" t="n"/>
       <c r="B103" s="8" t="n">
         <v>6</v>
@@ -25546,7 +25546,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="104" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="104" s="298">
       <c r="A104" s="20" t="inlineStr">
         <is>
           <t>Y</t>
@@ -25617,7 +25617,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="105" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="105" s="298">
       <c r="A105" s="369" t="n"/>
       <c r="B105" s="8" t="n">
         <v>7</v>
@@ -25675,7 +25675,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="106" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="106" s="298">
       <c r="A106" s="35" t="inlineStr">
         <is>
           <t>Z</t>
@@ -25737,7 +25737,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="107" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="107" s="298">
       <c r="A107" s="370" t="n"/>
       <c r="B107" s="8" t="n">
         <v>6</v>
@@ -25795,7 +25795,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="108" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="108" s="298">
       <c r="A108" s="370" t="n"/>
       <c r="B108" s="8" t="n">
         <v>6</v>
@@ -25853,7 +25853,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="109" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="109" s="298">
       <c r="A109" s="370" t="n"/>
       <c r="B109" s="8" t="n">
         <v>7</v>
@@ -25911,7 +25911,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="110" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="110" s="298">
       <c r="A110" s="369" t="n"/>
       <c r="B110" s="8" t="n">
         <v>7</v>
@@ -25970,7 +25970,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection autoFilter="1" deleteColumns="1" deleteRows="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertHyperlinks="1" insertRows="1" objects="1" pivotTables="1" scenarios="0" selectLockedCells="0" selectUnlockedCells="0" sheet="1" sort="1"/>
   <mergeCells count="23">
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A14"/>
@@ -25997,11 +25997,11 @@
     <mergeCell ref="A106:A110"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:M110">
-    <cfRule type="expression" priority="1" dxfId="1">
+    <cfRule dxfId="1" priority="1" type="expression">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -26015,19 +26015,19 @@
   <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.641666666666669" defaultRowHeight="14.25"/>
   <cols>
-    <col width="8.725" customWidth="1" style="1" min="1" max="2"/>
-    <col width="20.6333333333333" customWidth="1" style="1" min="3" max="3"/>
-    <col width="8.725" customWidth="1" style="1" min="4" max="4"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="5" max="5"/>
-    <col width="8.725" customWidth="1" style="1" min="6" max="6"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9.08333333333333" customWidth="1" style="1" min="8" max="8"/>
-    <col width="8.725" customWidth="1" style="2" min="9" max="10"/>
-    <col width="23.9583333333333" customWidth="1" style="1" min="11" max="11"/>
-    <col width="8.725" customWidth="1" style="1" min="12" max="256"/>
+    <col customWidth="1" max="2" min="1" style="1" width="8.725"/>
+    <col customWidth="1" max="3" min="3" style="1" width="20.6333333333333"/>
+    <col customWidth="1" max="4" min="4" style="1" width="8.725"/>
+    <col customWidth="1" max="5" min="5" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="6" min="6" style="1" width="8.725"/>
+    <col customWidth="1" max="7" min="7" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="8" min="8" style="1" width="9.08333333333333"/>
+    <col customWidth="1" max="10" min="9" style="2" width="8.725"/>
+    <col customWidth="1" max="11" min="11" style="1" width="23.9583333333333"/>
+    <col customWidth="1" max="256" min="12" style="1" width="8.725"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" customHeight="1" s="298">
+    <row customHeight="1" ht="40.5" r="1" s="298">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>音序</t>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="2" s="298">
       <c r="A2" s="35" t="inlineStr">
         <is>
           <t>*</t>
@@ -26157,7 +26157,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="3" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="3" s="298">
       <c r="A3" s="370" t="n"/>
       <c r="B3" s="8" t="n">
         <v>9</v>
@@ -26215,7 +26215,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="4" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="4" s="298">
       <c r="A4" s="370" t="n"/>
       <c r="B4" s="8" t="n">
         <v>9</v>
@@ -26273,7 +26273,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="5" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="5" s="298">
       <c r="A5" s="369" t="n"/>
       <c r="B5" s="8" t="n">
         <v>9</v>
@@ -26340,7 +26340,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="6" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="6" s="298">
       <c r="A6" s="20" t="inlineStr">
         <is>
           <t>A</t>
@@ -26402,7 +26402,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="7" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="7" s="298">
       <c r="A7" s="370" t="n"/>
       <c r="B7" s="8" t="n">
         <v>9</v>
@@ -26460,7 +26460,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="8" ht="94.5" customHeight="1" s="298">
+    <row customHeight="1" ht="94.5" r="8" s="298">
       <c r="A8" s="369" t="n"/>
       <c r="B8" s="8" t="n">
         <v>9</v>
@@ -26528,7 +26528,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="9" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="9" s="298">
       <c r="A9" s="20" t="inlineStr">
         <is>
           <t>B</t>
@@ -26590,7 +26590,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="10" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="10" s="298">
       <c r="A10" s="370" t="n"/>
       <c r="B10" s="8" t="n">
         <v>8</v>
@@ -26648,7 +26648,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="11" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="11" s="298">
       <c r="A11" s="370" t="n"/>
       <c r="B11" s="8" t="n">
         <v>9</v>
@@ -26706,7 +26706,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="12" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="12" s="298">
       <c r="A12" s="370" t="n"/>
       <c r="B12" s="8" t="n">
         <v>9</v>
@@ -26764,7 +26764,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="13" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="13" s="298">
       <c r="A13" s="370" t="n"/>
       <c r="B13" s="8" t="n">
         <v>8</v>
@@ -26822,7 +26822,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="14" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="14" s="298">
       <c r="A14" s="370" t="n"/>
       <c r="B14" s="8" t="n">
         <v>9</v>
@@ -26880,7 +26880,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="15" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="15" s="298">
       <c r="A15" s="370" t="n"/>
       <c r="B15" s="8" t="n">
         <v>8</v>
@@ -26938,7 +26938,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="16" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="16" s="298">
       <c r="A16" s="370" t="n"/>
       <c r="B16" s="8" t="n">
         <v>9</v>
@@ -26996,7 +26996,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="17" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="17" s="298">
       <c r="A17" s="369" t="n"/>
       <c r="B17" s="8" t="n">
         <v>9</v>
@@ -27054,7 +27054,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="18" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="18" s="298">
       <c r="A18" s="20" t="inlineStr">
         <is>
           <t>C</t>
@@ -27116,7 +27116,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="19" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="19" s="298">
       <c r="A19" s="370" t="n"/>
       <c r="B19" s="8" t="n">
         <v>9</v>
@@ -27174,7 +27174,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="20" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="20" s="298">
       <c r="A20" s="370" t="n"/>
       <c r="B20" s="8" t="n">
         <v>10</v>
@@ -27232,7 +27232,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="21" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="21" s="298">
       <c r="A21" s="370" t="n"/>
       <c r="B21" s="8" t="n">
         <v>9</v>
@@ -27290,7 +27290,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="22" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="22" s="298">
       <c r="A22" s="370" t="n"/>
       <c r="B22" s="8" t="n">
         <v>10</v>
@@ -27348,7 +27348,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="23" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="23" s="298">
       <c r="A23" s="369" t="n"/>
       <c r="B23" s="8" t="n">
         <v>9</v>
@@ -27406,7 +27406,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="24" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="24" s="298">
       <c r="A24" s="20" t="inlineStr">
         <is>
           <t>D</t>
@@ -27468,7 +27468,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="25" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="25" s="298">
       <c r="A25" s="370" t="n"/>
       <c r="B25" s="8" t="n">
         <v>10</v>
@@ -27526,7 +27526,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="26" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="26" s="298">
       <c r="A26" s="370" t="n"/>
       <c r="B26" s="8" t="n">
         <v>10</v>
@@ -27584,7 +27584,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="27" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="27" s="298">
       <c r="A27" s="369" t="n"/>
       <c r="B27" s="8" t="n">
         <v>9</v>
@@ -27642,7 +27642,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="28" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="28" s="298">
       <c r="A28" s="20" t="inlineStr">
         <is>
           <t>F</t>
@@ -27704,7 +27704,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="29" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="29" s="298">
       <c r="A29" s="370" t="n"/>
       <c r="B29" s="8" t="n">
         <v>9</v>
@@ -27762,7 +27762,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="30" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="30" s="298">
       <c r="A30" s="370" t="n"/>
       <c r="B30" s="8" t="n">
         <v>9</v>
@@ -27820,7 +27820,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="31" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="31" s="298">
       <c r="A31" s="370" t="n"/>
       <c r="B31" s="8" t="n">
         <v>10</v>
@@ -27878,7 +27878,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="32" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="32" s="298">
       <c r="A32" s="370" t="n"/>
       <c r="B32" s="8" t="n">
         <v>8</v>
@@ -27936,7 +27936,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="33" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="33" s="298">
       <c r="A33" s="369" t="n"/>
       <c r="B33" s="8" t="n">
         <v>8</v>
@@ -27994,7 +27994,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="34" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="34" s="298">
       <c r="A34" s="20" t="inlineStr">
         <is>
           <t>G</t>
@@ -28056,7 +28056,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="35" ht="72" customHeight="1" s="298">
+    <row customHeight="1" ht="72" r="35" s="298">
       <c r="A35" s="370" t="n"/>
       <c r="B35" s="8" t="n">
         <v>8</v>
@@ -28123,7 +28123,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="36" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="36" s="298">
       <c r="A36" s="370" t="n"/>
       <c r="B36" s="8" t="n">
         <v>10</v>
@@ -28181,7 +28181,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="37" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="37" s="298">
       <c r="A37" s="370" t="n"/>
       <c r="B37" s="8" t="n">
         <v>10</v>
@@ -28239,7 +28239,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="38" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="38" s="298">
       <c r="A38" s="369" t="n"/>
       <c r="B38" s="8" t="n">
         <v>10</v>
@@ -28297,7 +28297,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="39" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="39" s="298">
       <c r="A39" s="20" t="inlineStr">
         <is>
           <t>H</t>
@@ -28359,7 +28359,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="40" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="40" s="298">
       <c r="A40" s="370" t="n"/>
       <c r="B40" s="8" t="n">
         <v>9</v>
@@ -28417,7 +28417,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="41" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="41" s="298">
       <c r="A41" s="370" t="n"/>
       <c r="B41" s="8" t="n">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="42" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="42" s="298">
       <c r="A42" s="370" t="n"/>
       <c r="B42" s="8" t="n">
         <v>8</v>
@@ -28533,7 +28533,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="43" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="43" s="298">
       <c r="A43" s="370" t="n"/>
       <c r="B43" s="8" t="n">
         <v>9</v>
@@ -28591,7 +28591,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="44" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="44" s="298">
       <c r="A44" s="370" t="n"/>
       <c r="B44" s="8" t="n">
         <v>8</v>
@@ -28649,7 +28649,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="45" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="45" s="298">
       <c r="A45" s="369" t="n"/>
       <c r="B45" s="8" t="n">
         <v>8</v>
@@ -28707,7 +28707,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="46" ht="36" customHeight="1" s="298">
+    <row customHeight="1" ht="36" r="46" s="298">
       <c r="A46" s="20" t="inlineStr">
         <is>
           <t>I</t>
@@ -28769,7 +28769,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="47" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="47" s="298">
       <c r="A47" s="20" t="inlineStr">
         <is>
           <t>J</t>
@@ -28831,7 +28831,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="48" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="48" s="298">
       <c r="A48" s="370" t="n"/>
       <c r="B48" s="8" t="n">
         <v>10</v>
@@ -28889,7 +28889,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="49" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="49" s="298">
       <c r="A49" s="370" t="n"/>
       <c r="B49" s="8" t="n">
         <v>9</v>
@@ -28947,7 +28947,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="50" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="50" s="298">
       <c r="A50" s="370" t="n"/>
       <c r="B50" s="8" t="n">
         <v>9</v>
@@ -29005,7 +29005,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="51" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="51" s="298">
       <c r="A51" s="369" t="n"/>
       <c r="B51" s="8" t="n">
         <v>10</v>
@@ -29063,7 +29063,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="52" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="52" s="298">
       <c r="A52" s="20" t="inlineStr">
         <is>
           <t>K</t>
@@ -29125,7 +29125,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="53" s="298">
       <c r="A53" s="370" t="n"/>
       <c r="B53" s="8" t="n">
         <v>9</v>
@@ -29183,7 +29183,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="54" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="54" s="298">
       <c r="A54" s="370" t="n"/>
       <c r="B54" s="8" t="n">
         <v>10</v>
@@ -29241,7 +29241,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="55" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="55" s="298">
       <c r="A55" s="369" t="n"/>
       <c r="B55" s="8" t="n">
         <v>10</v>
@@ -29299,7 +29299,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="56" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="56" s="298">
       <c r="A56" s="20" t="inlineStr">
         <is>
           <t>L</t>
@@ -29361,7 +29361,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="57" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="57" s="298">
       <c r="A57" s="370" t="n"/>
       <c r="B57" s="8" t="n">
         <v>10</v>
@@ -29419,7 +29419,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="58" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="58" s="298">
       <c r="A58" s="370" t="n"/>
       <c r="B58" s="8" t="n">
         <v>8</v>
@@ -29477,7 +29477,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="59" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="59" s="298">
       <c r="A59" s="370" t="n"/>
       <c r="B59" s="8" t="n">
         <v>8</v>
@@ -29535,7 +29535,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="60" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="60" s="298">
       <c r="A60" s="370" t="n"/>
       <c r="B60" s="8" t="n">
         <v>10</v>
@@ -29593,7 +29593,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="61" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="61" s="298">
       <c r="A61" s="369" t="n"/>
       <c r="B61" s="8" t="n">
         <v>9</v>
@@ -29651,7 +29651,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="62" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="62" s="298">
       <c r="A62" s="20" t="inlineStr">
         <is>
           <t>M</t>
@@ -29713,7 +29713,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="63" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="63" s="298">
       <c r="A63" s="369" t="n"/>
       <c r="B63" s="8" t="n">
         <v>10</v>
@@ -29771,7 +29771,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="64" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="64" s="298">
       <c r="A64" s="35" t="inlineStr">
         <is>
           <t>N</t>
@@ -29833,7 +29833,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="65" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="65" s="298">
       <c r="A65" s="370" t="n"/>
       <c r="B65" s="8" t="n">
         <v>8</v>
@@ -29891,7 +29891,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="66" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="66" s="298">
       <c r="A66" s="370" t="n"/>
       <c r="B66" s="8" t="n">
         <v>9</v>
@@ -29949,7 +29949,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="67" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="67" s="298">
       <c r="A67" s="369" t="n"/>
       <c r="B67" s="8" t="n">
         <v>9</v>
@@ -30007,7 +30007,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="68" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="68" s="298">
       <c r="A68" s="20" t="inlineStr">
         <is>
           <t>O</t>
@@ -30069,7 +30069,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="69" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="69" s="298">
       <c r="A69" s="20" t="inlineStr">
         <is>
           <t>P</t>
@@ -30131,7 +30131,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="70" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="70" s="298">
       <c r="A70" s="370" t="n"/>
       <c r="B70" s="8" t="n">
         <v>10</v>
@@ -30189,7 +30189,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="71" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="71" s="298">
       <c r="A71" s="370" t="n"/>
       <c r="B71" s="8" t="n">
         <v>10</v>
@@ -30247,7 +30247,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="72" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="72" s="298">
       <c r="A72" s="370" t="n"/>
       <c r="B72" s="8" t="n">
         <v>9</v>
@@ -30305,7 +30305,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="73" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="73" s="298">
       <c r="A73" s="369" t="n"/>
       <c r="B73" s="8" t="n">
         <v>8</v>
@@ -30363,7 +30363,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="74" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="74" s="298">
       <c r="A74" s="20" t="inlineStr">
         <is>
           <t>Q</t>
@@ -30425,7 +30425,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="75" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="75" s="298">
       <c r="A75" s="370" t="n"/>
       <c r="B75" s="8" t="n">
         <v>8</v>
@@ -30483,7 +30483,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="76" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="76" s="298">
       <c r="A76" s="370" t="n"/>
       <c r="B76" s="8" t="n">
         <v>8</v>
@@ -30541,7 +30541,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="77" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="77" s="298">
       <c r="A77" s="369" t="n"/>
       <c r="B77" s="8" t="n">
         <v>9</v>
@@ -30599,7 +30599,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="78" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="78" s="298">
       <c r="A78" s="20" t="inlineStr">
         <is>
           <t>R</t>
@@ -30661,7 +30661,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="79" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="79" s="298">
       <c r="A79" s="370" t="n"/>
       <c r="B79" s="8" t="n">
         <v>9</v>
@@ -30719,7 +30719,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" ht="94.5" customHeight="1" s="298">
+    <row customHeight="1" ht="94.5" r="80" s="298">
       <c r="A80" s="369" t="n"/>
       <c r="B80" s="8" t="n">
         <v>8</v>
@@ -30786,7 +30786,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="81" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="81" s="298">
       <c r="A81" s="20" t="inlineStr">
         <is>
           <t>S</t>
@@ -30848,7 +30848,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="82" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="82" s="298">
       <c r="A82" s="370" t="n"/>
       <c r="B82" s="8" t="n">
         <v>9</v>
@@ -30906,7 +30906,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="83" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="83" s="298">
       <c r="A83" s="370" t="n"/>
       <c r="B83" s="8" t="n">
         <v>8</v>
@@ -30964,7 +30964,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="84" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="84" s="298">
       <c r="A84" s="370" t="n"/>
       <c r="B84" s="8" t="n">
         <v>9</v>
@@ -31022,7 +31022,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="85" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="85" s="298">
       <c r="A85" s="370" t="n"/>
       <c r="B85" s="8" t="n">
         <v>9</v>
@@ -31080,7 +31080,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="86" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="86" s="298">
       <c r="A86" s="370" t="n"/>
       <c r="B86" s="8" t="n">
         <v>9</v>
@@ -31138,7 +31138,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="87" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="87" s="298">
       <c r="A87" s="369" t="n"/>
       <c r="B87" s="8" t="n">
         <v>10</v>
@@ -31196,7 +31196,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="88" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="88" s="298">
       <c r="A88" s="20" t="inlineStr">
         <is>
           <t>T</t>
@@ -31258,7 +31258,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="89" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="89" s="298">
       <c r="A89" s="370" t="n"/>
       <c r="B89" s="8" t="n">
         <v>10</v>
@@ -31316,7 +31316,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="90" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="90" s="298">
       <c r="A90" s="370" t="n"/>
       <c r="B90" s="8" t="n">
         <v>8</v>
@@ -31374,7 +31374,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="91" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="91" s="298">
       <c r="A91" s="370" t="n"/>
       <c r="B91" s="8" t="n">
         <v>8</v>
@@ -31432,7 +31432,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="92" ht="63" customHeight="1" s="298">
+    <row customHeight="1" ht="63" r="92" s="298">
       <c r="A92" s="369" t="n"/>
       <c r="B92" s="8" t="n">
         <v>8</v>
@@ -31490,7 +31490,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="93" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="93" s="298">
       <c r="A93" s="20" t="inlineStr">
         <is>
           <t>V</t>
@@ -31552,7 +31552,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="94" ht="78.75" customHeight="1" s="298">
+    <row customHeight="1" ht="78.75" r="94" s="298">
       <c r="A94" s="369" t="n"/>
       <c r="B94" s="8" t="n">
         <v>10</v>
@@ -31610,7 +31610,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="95" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="95" s="298">
       <c r="A95" s="20" t="inlineStr">
         <is>
           <t>W</t>
@@ -31672,7 +31672,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="96" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="96" s="298">
       <c r="A96" s="370" t="n"/>
       <c r="B96" s="8" t="n">
         <v>9</v>
@@ -31730,7 +31730,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="97" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="97" s="298">
       <c r="A97" s="370" t="n"/>
       <c r="B97" s="8" t="n">
         <v>9</v>
@@ -31788,7 +31788,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="98" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="98" s="298">
       <c r="A98" s="370" t="n"/>
       <c r="B98" s="8" t="n">
         <v>8</v>
@@ -31846,7 +31846,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="99" s="298">
       <c r="A99" s="370" t="n"/>
       <c r="B99" s="8" t="n">
         <v>8</v>
@@ -31904,7 +31904,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="100" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="100" s="298">
       <c r="A100" s="370" t="n"/>
       <c r="B100" s="8" t="n">
         <v>8</v>
@@ -31962,7 +31962,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="101" ht="94.5" customHeight="1" s="298">
+    <row customHeight="1" ht="94.5" r="101" s="298">
       <c r="A101" s="370" t="n"/>
       <c r="B101" s="8" t="n">
         <v>8</v>
@@ -32029,7 +32029,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="102" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="102" s="298">
       <c r="A102" s="369" t="n"/>
       <c r="B102" s="8" t="n">
         <v>9</v>
@@ -32087,7 +32087,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="103" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="103" s="298">
       <c r="A103" s="35" t="inlineStr">
         <is>
           <t>X</t>
@@ -32149,7 +32149,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="104" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="104" s="298">
       <c r="A104" s="369" t="n"/>
       <c r="B104" s="8" t="n">
         <v>8</v>
@@ -32207,7 +32207,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="105" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="105" s="298">
       <c r="A105" s="20" t="inlineStr">
         <is>
           <t>Y</t>
@@ -32269,7 +32269,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="106" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="106" s="298">
       <c r="A106" s="370" t="n"/>
       <c r="B106" s="8" t="n">
         <v>10</v>
@@ -32327,7 +32327,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="107" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="107" s="298">
       <c r="A107" s="370" t="n"/>
       <c r="B107" s="8" t="n">
         <v>9</v>
@@ -32385,7 +32385,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="108" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="108" s="298">
       <c r="A108" s="370" t="n"/>
       <c r="B108" s="8" t="n">
         <v>9</v>
@@ -32443,7 +32443,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="109" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="109" s="298">
       <c r="A109" s="370" t="n"/>
       <c r="B109" s="8" t="n">
         <v>9</v>
@@ -32501,7 +32501,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="110" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="110" s="298">
       <c r="A110" s="369" t="n"/>
       <c r="B110" s="8" t="n">
         <v>8</v>
@@ -32559,7 +32559,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="111" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="111" s="298">
       <c r="A111" s="35" t="inlineStr">
         <is>
           <t>Z</t>
@@ -32621,7 +32621,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="112" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="112" s="298">
       <c r="A112" s="370" t="n"/>
       <c r="B112" s="8" t="n">
         <v>10</v>
@@ -32679,7 +32679,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="113" ht="47.25" customHeight="1" s="298">
+    <row customHeight="1" ht="47.25" r="113" s="298">
       <c r="A113" s="370" t="n"/>
       <c r="B113" s="8" t="n">
         <v>10</v>
@@ -32737,7 +32737,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="114" ht="31.5" customHeight="1" s="298">
+    <row customHeight="1" ht="31.5" r="114" s="298">
       <c r="A114" s="369" t="n"/>
       <c r="B114" s="8" t="n">
         <v>9</v>
@@ -32796,7 +32796,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection autoFilter="1" deleteColumns="1" deleteRows="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertHyperlinks="1" insertRows="1" objects="1" pivotTables="1" scenarios="0" selectLockedCells="0" selectUnlockedCells="0" sheet="1" sort="1"/>
   <mergeCells count="23">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A8"/>
@@ -32823,21 +32823,21 @@
     <mergeCell ref="A111:A114"/>
   </mergeCells>
   <conditionalFormatting sqref="F88">
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule dxfId="1" priority="2" type="expression">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G88">
-    <cfRule type="expression" priority="1" dxfId="1">
+    <cfRule dxfId="1" priority="1" type="expression">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:M87 B88:E88 H88:M88 B89:M114">
-    <cfRule type="expression" priority="3" dxfId="1">
+    <cfRule dxfId="1" priority="3" type="expression">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>